--- a/BIRK.xlsx
+++ b/BIRK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD70B21-FEBD-4820-ABAA-2D04A16E24EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C863D295-C86A-419B-8A6B-3E4E4090B42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{18F8973A-4B1D-45B3-BBD1-81233DF5C159}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{18F8973A-4B1D-45B3-BBD1-81233DF5C159}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t>Birkenstock Holding</t>
   </si>
@@ -198,9 +198,6 @@
     <t>Tax Rate</t>
   </si>
   <si>
-    <t>Corporate/other Growth</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -233,6 +230,18 @@
   <si>
     <t>Alexandre Arnault &amp; other</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -241,13 +250,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -318,28 +333,28 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -693,10 +708,10 @@
         <v>45</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I2" s="2">
-        <v>42.57</v>
+        <v>39.659999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -705,7 +720,7 @@
       </c>
       <c r="I3" s="11">
         <f>+I2*I10</f>
-        <v>36.1845</v>
+        <v>33.710999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -715,8 +730,8 @@
       <c r="I4" s="3">
         <v>183.90605600000001</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>11</v>
+      <c r="J4" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -728,7 +743,7 @@
       </c>
       <c r="I5" s="3">
         <f>+I3*I4</f>
-        <v>6654.5486833320001</v>
+        <v>6199.6570538160004</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -739,10 +754,10 @@
         <v>23</v>
       </c>
       <c r="I6" s="3">
-        <v>329.06700000000001</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>11</v>
+        <v>229.227</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -750,11 +765,11 @@
         <v>24</v>
       </c>
       <c r="I7" s="3">
-        <f>1128.01+4.202+17.133</f>
-        <v>1149.345</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>11</v>
+        <f>1128.819+11.389</f>
+        <v>1140.2079999999999</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -763,55 +778,55 @@
       </c>
       <c r="I8" s="3">
         <f>+I5-I6+I7</f>
-        <v>7474.8266833320004</v>
+        <v>7110.6380538160001</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I10" s="2">
         <v>0.85</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H12" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I12" s="12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H12" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="13" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H13" s="12" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H13" s="13" t="s">
+      <c r="I13" s="12" t="s">
         <v>63</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J16" s="13"/>
+        <v>54</v>
+      </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +839,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05227C9-86FF-4681-812C-4D0390C0B72A}">
-  <dimension ref="A1:AU316"/>
+  <dimension ref="A1:AY315"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -832,12 +847,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
@@ -862,33 +877,45 @@
       <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
@@ -902,7 +929,7 @@
         <v>340.59300000000002</v>
       </c>
       <c r="F3" s="3">
-        <f>+R3-SUM(C3:E3)</f>
+        <f>+V3-SUM(C3:E3)</f>
         <v>240.19399999999996</v>
       </c>
       <c r="G3" s="3">
@@ -915,30 +942,32 @@
         <v>390.15600000000001</v>
       </c>
       <c r="J3" s="3">
-        <f>+S3-SUM(G3:I3)</f>
+        <f>+W3-SUM(G3:I3)</f>
         <v>293.24800000000005</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>215.12299999999999</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="3">
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3">
         <v>772.88300000000004</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="U3" s="3">
         <v>887.95699999999999</v>
       </c>
-      <c r="R3" s="3">
+      <c r="V3" s="3">
         <v>1083.721</v>
       </c>
-      <c r="S3" s="3">
+      <c r="W3" s="3">
         <v>1297.933</v>
       </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
@@ -963,8 +992,12 @@
       <c r="AS3" s="3"/>
       <c r="AT3" s="3"/>
       <c r="AU3" s="3"/>
-    </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV3" s="3"/>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AY3" s="3"/>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
@@ -978,7 +1011,7 @@
         <v>223.364</v>
       </c>
       <c r="F4" s="3">
-        <f t="shared" ref="F4:F19" si="0">+R4-SUM(C4:E4)</f>
+        <f t="shared" ref="F4:F19" si="0">+V4-SUM(C4:E4)</f>
         <v>214.89499999999998</v>
       </c>
       <c r="G4" s="3">
@@ -991,30 +1024,32 @@
         <v>243.89099999999999</v>
       </c>
       <c r="J4" s="3">
-        <f t="shared" ref="J4:J8" si="1">+S4-SUM(G4:I4)</f>
+        <f t="shared" ref="J4:J8" si="1">+W4-SUM(G4:I4)</f>
         <v>231.68400000000008</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>186.18700000000001</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="3">
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3">
         <v>466.66800000000001</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="U4" s="3">
         <v>598.66399999999999</v>
       </c>
-      <c r="R4" s="3">
+      <c r="V4" s="3">
         <v>716.68700000000001</v>
       </c>
-      <c r="S4" s="3">
+      <c r="W4" s="3">
         <v>794.79700000000003</v>
       </c>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
@@ -1039,8 +1074,12 @@
       <c r="AS4" s="3"/>
       <c r="AT4" s="3"/>
       <c r="AU4" s="3"/>
-    </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV4" s="3"/>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
@@ -1070,27 +1109,29 @@
         <f t="shared" si="1"/>
         <v>250.18200000000002</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>221.774</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
-      <c r="P5" s="3">
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3">
         <v>667.38699999999994</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="U5" s="3">
         <v>804.69</v>
       </c>
-      <c r="R5" s="3">
+      <c r="V5" s="3">
         <v>943.71</v>
       </c>
-      <c r="S5" s="3">
+      <c r="W5" s="3">
         <v>1085.672</v>
       </c>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
@@ -1115,8 +1156,12 @@
       <c r="AS5" s="3"/>
       <c r="AT5" s="3"/>
       <c r="AU5" s="3"/>
-    </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV5" s="3"/>
+      <c r="AW5" s="3"/>
+      <c r="AX5" s="3"/>
+      <c r="AY5" s="3"/>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -1146,27 +1191,29 @@
         <f t="shared" si="1"/>
         <v>211.02300000000002</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>119.218</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
-      <c r="P6" s="3">
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3">
         <v>449.13099999999997</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="U6" s="3">
         <v>529.50699999999995</v>
       </c>
-      <c r="R6" s="3">
+      <c r="V6" s="3">
         <v>644.88800000000003</v>
       </c>
-      <c r="S6" s="3">
+      <c r="W6" s="3">
         <v>785.23</v>
       </c>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
@@ -1191,8 +1238,12 @@
       <c r="AS6" s="3"/>
       <c r="AT6" s="3"/>
       <c r="AU6" s="3"/>
-    </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV6" s="3"/>
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="3"/>
+      <c r="AY6" s="3"/>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
@@ -1222,27 +1273,29 @@
         <f t="shared" si="1"/>
         <v>63.727000000000004</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <v>60.317999999999998</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
-      <c r="P7" s="3">
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3">
         <v>123.033</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="U7" s="3">
         <v>152.42400000000001</v>
       </c>
-      <c r="R7" s="3">
+      <c r="V7" s="3">
         <v>211.81</v>
       </c>
-      <c r="S7" s="3">
+      <c r="W7" s="3">
         <v>221.828</v>
       </c>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
@@ -1267,8 +1320,12 @@
       <c r="AS7" s="3"/>
       <c r="AT7" s="3"/>
       <c r="AU7" s="3"/>
-    </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV7" s="3"/>
+      <c r="AW7" s="3"/>
+      <c r="AX7" s="3"/>
+      <c r="AY7" s="3"/>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
@@ -1298,27 +1355,29 @@
         <f t="shared" si="1"/>
         <v>1.4059999999999997</v>
       </c>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>0.59099999999999997</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="3">
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3">
         <v>3.282</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>5.29</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>4.282</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>4.6989999999999998</v>
       </c>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
@@ -1343,8 +1402,12 @@
       <c r="AS8" s="3"/>
       <c r="AT8" s="3"/>
       <c r="AU8" s="3"/>
-    </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV8" s="3"/>
+      <c r="AW8" s="3"/>
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="3"/>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1358,7 +1421,7 @@
         <v>564.75800000000004</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" ref="F9:Q9" si="2">+SUM(F5:F8)</f>
+        <f t="shared" ref="F9:U9" si="2">+SUM(F5:F8)</f>
         <v>455.76400000000001</v>
       </c>
       <c r="G9" s="7">
@@ -1374,43 +1437,45 @@
         <f t="shared" si="2"/>
         <v>526.33799999999997</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7">
+      <c r="K9" s="7">
+        <v>401.90199999999999</v>
+      </c>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M9" s="7">
+      <c r="Q9" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N9" s="7">
+      <c r="R9" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O9" s="7">
+      <c r="S9" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P9" s="7">
+      <c r="T9" s="7">
         <f t="shared" si="2"/>
         <v>1242.8329999999999</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="U9" s="7">
         <f t="shared" si="2"/>
         <v>1491.9110000000001</v>
       </c>
-      <c r="R9" s="7">
-        <f>+SUM(R5:R8)</f>
+      <c r="V9" s="7">
+        <f>+SUM(V5:V8)</f>
         <v>1804.6899999999998</v>
       </c>
-      <c r="S9" s="7">
-        <f>+SUM(S5:S8)</f>
+      <c r="W9" s="7">
+        <f>+SUM(W5:W8)</f>
         <v>2097.4290000000001</v>
       </c>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
@@ -1435,8 +1500,12 @@
       <c r="AS9" s="3"/>
       <c r="AT9" s="3"/>
       <c r="AU9" s="3"/>
-    </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV9" s="3"/>
+      <c r="AW9" s="3"/>
+      <c r="AX9" s="3"/>
+      <c r="AY9" s="3"/>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
@@ -1463,30 +1532,32 @@
         <v>250.964</v>
       </c>
       <c r="J10" s="3">
-        <f>+S10-SUM(G10:I10)</f>
+        <f>+W10-SUM(G10:I10)</f>
         <v>220.31799999999998</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>177.95599999999999</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="3">
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3">
         <v>493.03100000000001</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>566.11800000000005</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>744.01300000000003</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>857.72299999999996</v>
       </c>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
@@ -1511,13 +1582,17 @@
       <c r="AS10" s="3"/>
       <c r="AT10" s="3"/>
       <c r="AU10" s="3"/>
-    </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV10" s="3"/>
+      <c r="AW10" s="3"/>
+      <c r="AX10" s="3"/>
+      <c r="AY10" s="3"/>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" ref="C11:J11" si="3">+C9-C10</f>
+        <f t="shared" ref="C11:K11" si="3">+C9-C10</f>
         <v>184.86799999999999</v>
       </c>
       <c r="D11" s="3">
@@ -1548,43 +1623,46 @@
         <f t="shared" si="3"/>
         <v>306.02</v>
       </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3">
-        <f t="shared" ref="L11:Q11" si="4">+L9-L10</f>
+      <c r="K11" s="3">
+        <f t="shared" si="3"/>
+        <v>223.946</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3">
+        <f t="shared" ref="P11:U11" si="4">+P9-P10</f>
         <v>0</v>
       </c>
-      <c r="M11" s="3">
+      <c r="Q11" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N11" s="3">
+      <c r="R11" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O11" s="3">
+      <c r="S11" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P11" s="3">
+      <c r="T11" s="3">
         <f t="shared" si="4"/>
         <v>749.80199999999991</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="U11" s="3">
         <f t="shared" si="4"/>
         <v>925.79300000000001</v>
       </c>
-      <c r="R11" s="3">
-        <f>+R9-R10</f>
+      <c r="V11" s="3">
+        <f>+V9-V10</f>
         <v>1060.6769999999997</v>
       </c>
-      <c r="S11" s="3">
-        <f t="shared" ref="S11" si="5">+S9-S10</f>
+      <c r="W11" s="3">
+        <f t="shared" ref="W11" si="5">+W9-W10</f>
         <v>1239.7060000000001</v>
       </c>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
@@ -1609,8 +1687,12 @@
       <c r="AS11" s="3"/>
       <c r="AT11" s="3"/>
       <c r="AU11" s="3"/>
-    </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV11" s="3"/>
+      <c r="AW11" s="3"/>
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="3"/>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>35</v>
       </c>
@@ -1637,30 +1719,32 @@
         <v>162.77099999999999</v>
       </c>
       <c r="J12" s="3">
-        <f>+S12-SUM(G12:I12)</f>
+        <f>+W12-SUM(G12:I12)</f>
         <v>156.23900000000003</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>125.58</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="3">
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3">
         <v>347.37099999999998</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="U12" s="3">
         <v>455.851</v>
       </c>
-      <c r="R12" s="3">
+      <c r="V12" s="3">
         <v>507.12200000000001</v>
       </c>
-      <c r="S12" s="3">
+      <c r="W12" s="3">
         <v>563.66600000000005</v>
       </c>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
@@ -1685,8 +1769,12 @@
       <c r="AS12" s="3"/>
       <c r="AT12" s="3"/>
       <c r="AU12" s="3"/>
-    </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV12" s="3"/>
+      <c r="AW12" s="3"/>
+      <c r="AX12" s="3"/>
+      <c r="AY12" s="3"/>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
@@ -1713,30 +1801,32 @@
         <v>32.96</v>
       </c>
       <c r="J13" s="3">
-        <f>+S13-SUM(G13:I13)</f>
+        <f>+W13-SUM(G13:I13)</f>
         <v>35.64800000000001</v>
       </c>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <v>29.265999999999998</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="3">
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3">
         <v>86.588999999999999</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="U13" s="3">
         <v>171.38800000000001</v>
       </c>
-      <c r="R13" s="3">
+      <c r="V13" s="3">
         <v>113.444</v>
       </c>
-      <c r="S13" s="3">
+      <c r="W13" s="3">
         <v>125.15900000000001</v>
       </c>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -1761,8 +1851,12 @@
       <c r="AS13" s="3"/>
       <c r="AT13" s="3"/>
       <c r="AU13" s="3"/>
-    </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV13" s="3"/>
+      <c r="AW13" s="3"/>
+      <c r="AX13" s="3"/>
+      <c r="AY13" s="3"/>
+    </row>
+    <row r="14" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
@@ -1789,30 +1883,32 @@
         <v>-9.5069999999999997</v>
       </c>
       <c r="J14" s="3">
-        <f>+S14-SUM(G14:I14)</f>
+        <f>+W14-SUM(G14:I14)</f>
         <v>2.1589999999999998</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>3.238</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="3">
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3">
         <v>-45.515999999999998</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <v>36.055999999999997</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <v>19.640999999999998</v>
       </c>
-      <c r="S14" s="3">
+      <c r="W14" s="3">
         <v>1.9530000000000001</v>
       </c>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
@@ -1837,8 +1933,12 @@
       <c r="AS14" s="3"/>
       <c r="AT14" s="3"/>
       <c r="AU14" s="3"/>
-    </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV14" s="3"/>
+      <c r="AW14" s="3"/>
+      <c r="AX14" s="3"/>
+      <c r="AY14" s="3"/>
+    </row>
+    <row r="15" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
@@ -1865,30 +1965,32 @@
         <v>0.127</v>
       </c>
       <c r="J15" s="3">
-        <f>+S15-SUM(G15:I15)</f>
+        <f>+W15-SUM(G15:I15)</f>
         <v>0.23599999999999999</v>
       </c>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>12.472</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="3">
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3">
         <v>1.669</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="U15" s="3">
         <v>-1.81</v>
       </c>
-      <c r="R15" s="3">
+      <c r="V15" s="3">
         <v>0.61199999999999999</v>
       </c>
-      <c r="S15" s="3">
+      <c r="W15" s="3">
         <v>0.61599999999999999</v>
       </c>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -1913,13 +2015,17 @@
       <c r="AS15" s="3"/>
       <c r="AT15" s="3"/>
       <c r="AU15" s="3"/>
-    </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV15" s="3"/>
+      <c r="AW15" s="3"/>
+      <c r="AX15" s="3"/>
+      <c r="AY15" s="3"/>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" ref="C16:J16" si="6">+C11-SUM(C12:C14)+C15</f>
+        <f t="shared" ref="C16:K16" si="6">+C11-SUM(C12:C14)+C15</f>
         <v>35.569999999999993</v>
       </c>
       <c r="D16" s="3">
@@ -1950,43 +2056,46 @@
         <f t="shared" si="6"/>
         <v>112.20999999999994</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3">
-        <f t="shared" ref="L16:Q16" si="7">+L11-SUM(L12:L14)+L15</f>
+      <c r="K16" s="3">
+        <f t="shared" si="6"/>
+        <v>78.333999999999989</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3">
+        <f t="shared" ref="P16:U16" si="7">+P11-SUM(P12:P14)+P15</f>
         <v>0</v>
       </c>
-      <c r="M16" s="3">
+      <c r="Q16" s="3">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N16" s="3">
+      <c r="R16" s="3">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O16" s="3">
+      <c r="S16" s="3">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P16" s="3">
+      <c r="T16" s="3">
         <f t="shared" si="7"/>
         <v>363.02699999999993</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="U16" s="3">
         <f t="shared" si="7"/>
         <v>260.68799999999993</v>
       </c>
-      <c r="R16" s="3">
-        <f>+R11-SUM(R12:R14)+R15</f>
+      <c r="V16" s="3">
+        <f>+V11-SUM(V12:V14)+V15</f>
         <v>421.08199999999971</v>
       </c>
-      <c r="S16" s="3">
-        <f t="shared" ref="S16" si="8">+S11-SUM(S12:S14)+S15</f>
+      <c r="W16" s="3">
+        <f t="shared" ref="W16" si="8">+W11-SUM(W12:W14)+W15</f>
         <v>549.5440000000001</v>
       </c>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -2011,8 +2120,12 @@
       <c r="AS16" s="3"/>
       <c r="AT16" s="3"/>
       <c r="AU16" s="3"/>
-    </row>
-    <row r="17" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV16" s="3"/>
+      <c r="AW16" s="3"/>
+      <c r="AX16" s="3"/>
+      <c r="AY16" s="3"/>
+    </row>
+    <row r="17" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
@@ -2039,30 +2152,32 @@
         <v>18.302</v>
       </c>
       <c r="J17" s="3">
-        <f>+S17-SUM(G17:I17)</f>
+        <f>+W17-SUM(G17:I17)</f>
         <v>10.871999999999986</v>
       </c>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3">
+        <v>9.1489999999999991</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
-      <c r="P17" s="3">
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3">
         <v>112.503</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>107.036</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>127.3</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>79.563999999999993</v>
       </c>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
@@ -2087,13 +2202,17 @@
       <c r="AS17" s="3"/>
       <c r="AT17" s="3"/>
       <c r="AU17" s="3"/>
-    </row>
-    <row r="18" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV17" s="3"/>
+      <c r="AW17" s="3"/>
+      <c r="AX17" s="3"/>
+      <c r="AY17" s="3"/>
+    </row>
+    <row r="18" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" ref="C18:J18" si="9">+C16-C17</f>
+        <f t="shared" ref="C18:K18" si="9">+C16-C17</f>
         <v>-0.48000000000000398</v>
       </c>
       <c r="D18" s="3">
@@ -2124,43 +2243,46 @@
         <f t="shared" si="9"/>
         <v>101.33799999999995</v>
       </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3">
-        <f t="shared" ref="L18:Q18" si="10">+L16-L17</f>
+      <c r="K18" s="3">
+        <f t="shared" si="9"/>
+        <v>69.184999999999988</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3">
+        <f t="shared" ref="P18" si="10">+P16-P17</f>
         <v>0</v>
       </c>
-      <c r="M18" s="3">
-        <f t="shared" si="10"/>
+      <c r="Q18" s="3">
+        <f t="shared" ref="Q18:U18" si="11">+Q16-Q17</f>
         <v>0</v>
       </c>
-      <c r="N18" s="3">
-        <f t="shared" si="10"/>
+      <c r="R18" s="3">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O18" s="3">
-        <f t="shared" si="10"/>
+      <c r="S18" s="3">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P18" s="3">
-        <f t="shared" si="10"/>
+      <c r="T18" s="3">
+        <f t="shared" si="11"/>
         <v>250.52399999999994</v>
       </c>
-      <c r="Q18" s="3">
-        <f t="shared" si="10"/>
+      <c r="U18" s="3">
+        <f t="shared" si="11"/>
         <v>153.65199999999993</v>
       </c>
-      <c r="R18" s="3">
-        <f>+R16-R17</f>
+      <c r="V18" s="3">
+        <f>+V16-V17</f>
         <v>293.7819999999997</v>
       </c>
-      <c r="S18" s="3">
-        <f t="shared" ref="S18" si="11">+S16-S17</f>
+      <c r="W18" s="3">
+        <f t="shared" ref="W18" si="12">+W16-W17</f>
         <v>469.98000000000013</v>
       </c>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
@@ -2185,8 +2307,12 @@
       <c r="AS18" s="3"/>
       <c r="AT18" s="3"/>
       <c r="AU18" s="3"/>
-    </row>
-    <row r="19" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV18" s="3"/>
+      <c r="AW18" s="3"/>
+      <c r="AX18" s="3"/>
+      <c r="AY18" s="3"/>
+    </row>
+    <row r="19" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>42</v>
       </c>
@@ -2213,30 +2339,32 @@
         <v>50.451000000000001</v>
       </c>
       <c r="J19" s="3">
-        <f>+S19-SUM(G19:I19)</f>
+        <f>+W19-SUM(G19:I19)</f>
         <v>7.4710000000000178</v>
       </c>
-      <c r="K19" s="3"/>
+      <c r="K19" s="3">
+        <v>18.626999999999999</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="3">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3">
         <v>63.412999999999997</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="U19" s="3">
         <v>78.63</v>
       </c>
-      <c r="R19" s="3">
+      <c r="V19" s="3">
         <v>102.18</v>
       </c>
-      <c r="S19" s="3">
+      <c r="W19" s="3">
         <v>121.65300000000001</v>
       </c>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
@@ -2261,80 +2389,87 @@
       <c r="AS19" s="3"/>
       <c r="AT19" s="3"/>
       <c r="AU19" s="3"/>
-    </row>
-    <row r="20" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV19" s="3"/>
+      <c r="AW19" s="3"/>
+      <c r="AX19" s="3"/>
+      <c r="AY19" s="3"/>
+    </row>
+    <row r="20" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:J20" si="12">+C18-C19</f>
+        <f t="shared" ref="C20:K20" si="13">+C18-C19</f>
         <v>-7.1540000000000044</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>71.652000000000029</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>74.669500000000042</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>52.434499999999915</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20.118999999999975</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>105.11300000000007</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>129.22800000000007</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>93.866999999999933</v>
       </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3">
-        <f t="shared" ref="L20:Q20" si="13">+L18-L19</f>
+      <c r="K20" s="3">
+        <f t="shared" si="13"/>
+        <v>50.557999999999993</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3">
+        <f t="shared" ref="P20:U20" si="14">+P18-P19</f>
         <v>0</v>
       </c>
-      <c r="M20" s="3">
-        <f t="shared" si="13"/>
+      <c r="Q20" s="3">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N20" s="3">
-        <f t="shared" si="13"/>
+      <c r="R20" s="3">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O20" s="3">
-        <f t="shared" si="13"/>
+      <c r="S20" s="3">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="P20" s="3">
-        <f t="shared" si="13"/>
+      <c r="T20" s="3">
+        <f t="shared" si="14"/>
         <v>187.11099999999993</v>
       </c>
-      <c r="Q20" s="3">
-        <f t="shared" si="13"/>
+      <c r="U20" s="3">
+        <f t="shared" si="14"/>
         <v>75.021999999999935</v>
       </c>
-      <c r="R20" s="3">
-        <f>+R18-R19</f>
+      <c r="V20" s="3">
+        <f>+V18-V19</f>
         <v>191.60199999999969</v>
       </c>
-      <c r="S20" s="3">
-        <f t="shared" ref="S20" si="14">+S18-S19</f>
+      <c r="W20" s="3">
+        <f t="shared" ref="W20" si="15">+W18-W19</f>
         <v>348.32700000000011</v>
       </c>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
@@ -2359,8 +2494,12 @@
       <c r="AS20" s="3"/>
       <c r="AT20" s="3"/>
       <c r="AU20" s="3"/>
-    </row>
-    <row r="21" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV20" s="3"/>
+      <c r="AW20" s="3"/>
+      <c r="AX20" s="3"/>
+      <c r="AY20" s="3"/>
+    </row>
+    <row r="21" spans="2:51" x14ac:dyDescent="0.2">
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -2406,80 +2545,87 @@
       <c r="AS21" s="3"/>
       <c r="AT21" s="3"/>
       <c r="AU21" s="3"/>
-    </row>
-    <row r="22" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV21" s="3"/>
+      <c r="AW21" s="3"/>
+      <c r="AX21" s="3"/>
+      <c r="AY21" s="3"/>
+    </row>
+    <row r="22" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:J22" si="15">+C20/C23</f>
+        <f t="shared" ref="C22:K22" si="16">+C20/C23</f>
         <v>-3.8273026460271399E-2</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.38148156083011325</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.39754309164107926</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2795025571436256</v>
       </c>
       <c r="G22" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.10711326985246934</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.55962011700395797</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.6929882882147882</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.50328803914343101</v>
       </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="8" t="e">
-        <f>+L20/L23</f>
+      <c r="K22" s="8">
+        <f t="shared" si="16"/>
+        <v>0.27491209968637459</v>
+      </c>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="8" t="e">
+        <f>+P20/P23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M22" s="8" t="e">
-        <f t="shared" ref="M22:Q22" si="16">+M20/M23</f>
+      <c r="Q22" s="8" t="e">
+        <f t="shared" ref="Q22:U22" si="17">+Q20/Q23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N22" s="8" t="e">
-        <f t="shared" si="16"/>
+      <c r="R22" s="8" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O22" s="8" t="e">
-        <f t="shared" si="16"/>
+      <c r="S22" s="8" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P22" s="8">
-        <f t="shared" si="16"/>
+      <c r="T22" s="8">
+        <f t="shared" si="17"/>
         <v>1.0240236323973686</v>
       </c>
-      <c r="Q22" s="8">
-        <f t="shared" si="16"/>
+      <c r="U22" s="8">
+        <f t="shared" si="17"/>
         <v>0.41058142466084485</v>
       </c>
-      <c r="R22" s="8">
-        <f>+R20/R23</f>
+      <c r="V22" s="8">
+        <f>+V20/V23</f>
         <v>1.0213361232362843</v>
       </c>
-      <c r="S22" s="8">
-        <f>+S20/S23</f>
+      <c r="W22" s="8">
+        <f>+W20/W23</f>
         <v>1.8676298679058039</v>
       </c>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
@@ -2504,8 +2650,12 @@
       <c r="AS22" s="3"/>
       <c r="AT22" s="3"/>
       <c r="AU22" s="3"/>
-    </row>
-    <row r="23" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV22" s="3"/>
+      <c r="AW22" s="3"/>
+      <c r="AX22" s="3"/>
+      <c r="AY22" s="3"/>
+    </row>
+    <row r="23" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>21</v>
       </c>
@@ -2519,7 +2669,7 @@
         <v>187.827437</v>
       </c>
       <c r="F23" s="3">
-        <f>+R23</f>
+        <f>+V23</f>
         <v>187.599357</v>
       </c>
       <c r="G23" s="3">
@@ -2534,27 +2684,29 @@
       <c r="J23" s="3">
         <v>186.50751199999999</v>
       </c>
-      <c r="K23" s="3"/>
+      <c r="K23" s="3">
+        <v>183.90605600000001</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
-      <c r="P23" s="3">
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3">
         <v>182.72136900000001</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>182.72136900000001</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>187.599357</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>186.50751199999999</v>
       </c>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
@@ -2579,8 +2731,12 @@
       <c r="AS23" s="3"/>
       <c r="AT23" s="3"/>
       <c r="AU23" s="3"/>
-    </row>
-    <row r="24" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV23" s="3"/>
+      <c r="AW23" s="3"/>
+      <c r="AX23" s="3"/>
+      <c r="AY23" s="3"/>
+    </row>
+    <row r="24" spans="2:51" x14ac:dyDescent="0.2">
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -2626,8 +2782,12 @@
       <c r="AS24" s="3"/>
       <c r="AT24" s="3"/>
       <c r="AU24" s="3"/>
-    </row>
-    <row r="25" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV24" s="3"/>
+      <c r="AW24" s="3"/>
+      <c r="AX24" s="3"/>
+      <c r="AY24" s="3"/>
+    </row>
+    <row r="25" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>46</v>
       </c>
@@ -2640,51 +2800,54 @@
         <v>0.16118223451802938</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:J29" si="17">+H5/D5-1</f>
+        <f t="shared" ref="H25:K27" si="18">+H5/D5-1</f>
         <v>0.23018665910898028</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.10394004206953844</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.11021273952055965</v>
       </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="9" t="e">
-        <f t="shared" ref="M25:Q29" si="18">+M5/L5-1</f>
+      <c r="K25" s="9">
+        <f t="shared" si="18"/>
+        <v>5.2558139534883752E-2</v>
+      </c>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="9" t="e">
+        <f t="shared" ref="Q25:U27" si="19">+Q5/P5-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N25" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="R25" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O25" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="S25" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P25" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="T25" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q25" s="9">
-        <f t="shared" si="18"/>
+      <c r="U25" s="9">
+        <f t="shared" si="19"/>
         <v>0.20573220635103784</v>
       </c>
-      <c r="R25" s="9">
-        <f>+R5/Q5-1</f>
+      <c r="V25" s="9">
+        <f>+V5/U5-1</f>
         <v>0.17276218170972668</v>
       </c>
-      <c r="S25" s="9">
-        <f>+S5/R5-1</f>
+      <c r="W25" s="9">
+        <f>+W5/V5-1</f>
         <v>0.15042968708607507</v>
       </c>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
@@ -2709,8 +2872,12 @@
       <c r="AS25" s="3"/>
       <c r="AT25" s="3"/>
       <c r="AU25" s="3"/>
-    </row>
-    <row r="26" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV25" s="3"/>
+      <c r="AW25" s="3"/>
+      <c r="AX25" s="3"/>
+      <c r="AY25" s="3"/>
+    </row>
+    <row r="26" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>47</v>
       </c>
@@ -2719,55 +2886,58 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="9">
-        <f t="shared" ref="G26:G29" si="19">+G6/C6-1</f>
+        <f t="shared" ref="G26:G27" si="20">+G6/C6-1</f>
         <v>0.17401288730463382</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.12308000780924333</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.12903408892459223</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.52041529471947445</v>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="9" t="e">
+      <c r="K26" s="9">
         <f t="shared" si="18"/>
+        <v>0.16017088527525569</v>
+      </c>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N26" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="R26" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O26" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="S26" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P26" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="T26" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q26" s="9">
-        <f t="shared" si="18"/>
+      <c r="U26" s="9">
+        <f t="shared" si="19"/>
         <v>0.17895892289777371</v>
       </c>
-      <c r="R26" s="9">
-        <f t="shared" ref="R26:S29" si="20">+R6/Q6-1</f>
+      <c r="V26" s="9">
+        <f t="shared" ref="V26:W27" si="21">+V6/U6-1</f>
         <v>0.21790269061598821</v>
       </c>
-      <c r="S26" s="9">
-        <f t="shared" si="20"/>
+      <c r="W26" s="9">
+        <f t="shared" si="21"/>
         <v>0.21762228479984125</v>
       </c>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
@@ -2792,8 +2962,12 @@
       <c r="AS26" s="3"/>
       <c r="AT26" s="3"/>
       <c r="AU26" s="3"/>
-    </row>
-    <row r="27" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV26" s="3"/>
+      <c r="AW26" s="3"/>
+      <c r="AX26" s="3"/>
+      <c r="AY26" s="3"/>
+    </row>
+    <row r="27" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>48</v>
       </c>
@@ -2802,55 +2976,58 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="9">
+        <f t="shared" si="20"/>
+        <v>0.46811494826081534</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="18"/>
+        <v>0.30186213655668093</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="18"/>
+        <v>0.21393436323111215</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="18"/>
+        <v>-0.29931830676195714</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" si="18"/>
+        <v>0.28055537863830327</v>
+      </c>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="9" t="e">
         <f t="shared" si="19"/>
-        <v>0.46811494826081534</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" si="17"/>
-        <v>0.30186213655668093</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" si="17"/>
-        <v>0.21393436323111215</v>
-      </c>
-      <c r="J27" s="9">
-        <f t="shared" si="17"/>
-        <v>-0.29931830676195714</v>
-      </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="9" t="e">
-        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N27" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="R27" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="S27" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P27" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="T27" s="9" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q27" s="9">
-        <f t="shared" si="18"/>
+      <c r="U27" s="9">
+        <f t="shared" si="19"/>
         <v>0.23888712784374921</v>
       </c>
-      <c r="R27" s="9">
-        <f t="shared" si="20"/>
+      <c r="V27" s="9">
+        <f t="shared" si="21"/>
         <v>0.38961056001679517</v>
       </c>
-      <c r="S27" s="9">
-        <f t="shared" si="20"/>
+      <c r="W27" s="9">
+        <f t="shared" si="21"/>
         <v>4.7297105896794367E-2</v>
       </c>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
@@ -2875,65 +3052,72 @@
       <c r="AS27" s="3"/>
       <c r="AT27" s="3"/>
       <c r="AU27" s="3"/>
-    </row>
-    <row r="28" spans="2:47" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="9">
-        <f t="shared" si="19"/>
-        <v>-0.3776223776223776</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" si="17"/>
-        <v>0.20485744456177413</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" si="17"/>
-        <v>0.24219725343320841</v>
-      </c>
-      <c r="J28" s="9">
-        <f t="shared" si="17"/>
-        <v>1.0829629629629629</v>
-      </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="AV27" s="3"/>
+      <c r="AW27" s="3"/>
+      <c r="AX27" s="3"/>
+      <c r="AY27" s="3"/>
+    </row>
+    <row r="28" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="10">
+        <f>+G9/C9-1</f>
+        <v>0.19409158732883491</v>
+      </c>
+      <c r="H28" s="10">
+        <f>+H9/D9-1</f>
+        <v>0.19342786611365548</v>
+      </c>
+      <c r="I28" s="10">
+        <f>+I9/E9-1</f>
+        <v>0.12444976432383426</v>
+      </c>
+      <c r="J28" s="10">
+        <f>+J9/F9-1</f>
+        <v>0.1548476843278539</v>
+      </c>
+      <c r="K28" s="10">
+        <f>+K9/G9-1</f>
+        <v>0.1110889944957274</v>
+      </c>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="10" t="e">
+        <f>+Q9/P9-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N28" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="R28" s="10" t="e">
+        <f>+R9/Q9-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O28" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="S28" s="10" t="e">
+        <f>+S9/R9-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P28" s="9" t="e">
-        <f t="shared" si="18"/>
+      <c r="T28" s="10" t="e">
+        <f>+T9/S9-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q28" s="9">
-        <f t="shared" si="18"/>
-        <v>0.61182205971968306</v>
-      </c>
-      <c r="R28" s="9">
-        <f t="shared" si="20"/>
-        <v>-0.19054820415879015</v>
-      </c>
-      <c r="S28" s="9">
-        <f t="shared" si="20"/>
-        <v>9.7384399813171374E-2</v>
-      </c>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
+      <c r="U28" s="10">
+        <f>+U9/T9-1</f>
+        <v>0.20041147925747071</v>
+      </c>
+      <c r="V28" s="10">
+        <f>+V9/U9-1</f>
+        <v>0.20964990538979866</v>
+      </c>
+      <c r="W28" s="10">
+        <f>+W9/V9-1</f>
+        <v>0.16221013027168119</v>
+      </c>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
@@ -2958,65 +3142,87 @@
       <c r="AS28" s="3"/>
       <c r="AT28" s="3"/>
       <c r="AU28" s="3"/>
-    </row>
-    <row r="29" spans="2:47" x14ac:dyDescent="0.2">
-      <c r="B29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="10">
-        <f t="shared" si="19"/>
-        <v>0.19409158732883491</v>
-      </c>
-      <c r="H29" s="10">
-        <f t="shared" si="17"/>
-        <v>0.19342786611365548</v>
-      </c>
-      <c r="I29" s="10">
-        <f t="shared" si="17"/>
-        <v>0.12444976432383426</v>
-      </c>
-      <c r="J29" s="10">
-        <f t="shared" si="17"/>
-        <v>0.1548476843278539</v>
-      </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="10" t="e">
-        <f t="shared" si="18"/>
+      <c r="AV28" s="3"/>
+      <c r="AW28" s="3"/>
+      <c r="AX28" s="3"/>
+      <c r="AY28" s="3"/>
+    </row>
+    <row r="29" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="9">
+        <f t="shared" ref="C29:F29" si="22">+C11/C9</f>
+        <v>0.61027848569278109</v>
+      </c>
+      <c r="D29" s="9">
+        <f t="shared" si="22"/>
+        <v>0.56345637556000705</v>
+      </c>
+      <c r="E29" s="9">
+        <f t="shared" si="22"/>
+        <v>0.59481229128228386</v>
+      </c>
+      <c r="F29" s="9">
+        <f t="shared" si="22"/>
+        <v>0.58961216770082747</v>
+      </c>
+      <c r="G29" s="9">
+        <f>+G11/G9</f>
+        <v>0.60277176482297035</v>
+      </c>
+      <c r="H29" s="9">
+        <f>+H11/H9</f>
+        <v>0.57732314174777577</v>
+      </c>
+      <c r="I29" s="9">
+        <f>+I11/I9</f>
+        <v>0.60480724109586459</v>
+      </c>
+      <c r="J29" s="9">
+        <f>+J11/J9</f>
+        <v>0.58141346435180441</v>
+      </c>
+      <c r="K29" s="9">
+        <f>+K11/K9</f>
+        <v>0.55721544058004191</v>
+      </c>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="9" t="e">
+        <f t="shared" ref="P29:W29" si="23">+P11/P9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N29" s="10" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q29" s="9" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="10" t="e">
-        <f t="shared" si="18"/>
+      <c r="R29" s="9" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P29" s="10" t="e">
-        <f t="shared" si="18"/>
+      <c r="S29" s="9" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q29" s="10">
-        <f t="shared" si="18"/>
-        <v>0.20041147925747071</v>
-      </c>
-      <c r="R29" s="10">
-        <f t="shared" si="20"/>
-        <v>0.20964990538979866</v>
-      </c>
-      <c r="S29" s="10">
-        <f t="shared" si="20"/>
-        <v>0.16221013027168119</v>
-      </c>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
+      <c r="T29" s="9">
+        <f t="shared" si="23"/>
+        <v>0.60330068480640597</v>
+      </c>
+      <c r="U29" s="9">
+        <f t="shared" si="23"/>
+        <v>0.62054170791689311</v>
+      </c>
+      <c r="V29" s="9">
+        <f t="shared" si="23"/>
+        <v>0.58773362738198787</v>
+      </c>
+      <c r="W29" s="9">
+        <f t="shared" si="23"/>
+        <v>0.59105981656590045</v>
+      </c>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
@@ -3041,80 +3247,87 @@
       <c r="AS29" s="3"/>
       <c r="AT29" s="3"/>
       <c r="AU29" s="3"/>
-    </row>
-    <row r="30" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV29" s="3"/>
+      <c r="AW29" s="3"/>
+      <c r="AX29" s="3"/>
+      <c r="AY29" s="3"/>
+    </row>
+    <row r="30" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:F30" si="21">+C11/C9</f>
-        <v>0.61027848569278109</v>
+        <f t="shared" ref="C30:F30" si="24">+C16/C9</f>
+        <v>0.11742219170485005</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="21"/>
-        <v>0.56345637556000705</v>
+        <f t="shared" si="24"/>
+        <v>0.27535096541463377</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="21"/>
-        <v>0.59481229128228386</v>
+        <f t="shared" si="24"/>
+        <v>0.27529136373455537</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="21"/>
-        <v>0.58961216770082747</v>
+        <f t="shared" si="24"/>
+        <v>0.21398794112742545</v>
       </c>
       <c r="G30" s="9">
-        <f>+G11/G9</f>
-        <v>0.60277176482297035</v>
+        <f>+G16/G9</f>
+        <v>0.177015860377807</v>
       </c>
       <c r="H30" s="9">
-        <f>+H11/H9</f>
-        <v>0.57732314174777577</v>
+        <f>+H16/H9</f>
+        <v>0.30526526561384582</v>
       </c>
       <c r="I30" s="9">
-        <f>+I11/I9</f>
-        <v>0.60480724109586459</v>
+        <f>+I16/I9</f>
+        <v>0.31176048198386885</v>
       </c>
       <c r="J30" s="9">
-        <f>+J11/J9</f>
-        <v>0.58141346435180441</v>
-      </c>
-      <c r="K30" s="3"/>
-      <c r="L30" s="9" t="e">
-        <f t="shared" ref="L30:S30" si="22">+L11/L9</f>
+        <f>+J16/J9</f>
+        <v>0.21319000338185717</v>
+      </c>
+      <c r="K30" s="9">
+        <f>+K16/K9</f>
+        <v>0.19490821145453366</v>
+      </c>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="9" t="e">
+        <f t="shared" ref="P30:W30" si="25">+P16/P9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M30" s="9" t="e">
-        <f t="shared" si="22"/>
+      <c r="Q30" s="9" t="e">
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N30" s="9" t="e">
-        <f t="shared" si="22"/>
+      <c r="R30" s="9" t="e">
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O30" s="9" t="e">
-        <f t="shared" si="22"/>
+      <c r="S30" s="9" t="e">
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P30" s="9">
-        <f t="shared" si="22"/>
-        <v>0.60330068480640597</v>
-      </c>
-      <c r="Q30" s="9">
-        <f t="shared" si="22"/>
-        <v>0.62054170791689311</v>
-      </c>
-      <c r="R30" s="9">
-        <f t="shared" si="22"/>
-        <v>0.58773362738198787</v>
-      </c>
-      <c r="S30" s="9">
-        <f t="shared" si="22"/>
-        <v>0.59105981656590045</v>
-      </c>
-      <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
+      <c r="T30" s="9">
+        <f t="shared" si="25"/>
+        <v>0.29209636371097319</v>
+      </c>
+      <c r="U30" s="9">
+        <f t="shared" si="25"/>
+        <v>0.17473428374748889</v>
+      </c>
+      <c r="V30" s="9">
+        <f t="shared" si="25"/>
+        <v>0.23332649928796623</v>
+      </c>
+      <c r="W30" s="9">
+        <f t="shared" si="25"/>
+        <v>0.26200839217918703</v>
+      </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
@@ -3139,80 +3352,87 @@
       <c r="AS30" s="3"/>
       <c r="AT30" s="3"/>
       <c r="AU30" s="3"/>
-    </row>
-    <row r="31" spans="2:47" x14ac:dyDescent="0.2">
+      <c r="AV30" s="3"/>
+      <c r="AW30" s="3"/>
+      <c r="AX30" s="3"/>
+      <c r="AY30" s="3"/>
+    </row>
+    <row r="31" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="23">+C16/C9</f>
-        <v>0.11742219170485005</v>
+        <f t="shared" ref="C31:F31" si="26">+C19/C18</f>
+        <v>-13.904166666666551</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="23"/>
-        <v>0.27535096541463377</v>
+        <f t="shared" si="26"/>
+        <v>0.31839196362321864</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="23"/>
-        <v>0.27529136373455537</v>
+        <f t="shared" si="26"/>
+        <v>0.3266648631588438</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="23"/>
-        <v>0.21398794112742545</v>
+        <f t="shared" si="26"/>
+        <v>0.32986772317720037</v>
       </c>
       <c r="G31" s="9">
-        <f>+G16/G9</f>
-        <v>0.177015860377807</v>
+        <f>+G19/G18</f>
+        <v>0.48744013043921358</v>
       </c>
       <c r="H31" s="9">
-        <f>+H16/H9</f>
-        <v>0.30526526561384582</v>
+        <f>+H19/H18</f>
+        <v>0.29789394232888683</v>
       </c>
       <c r="I31" s="9">
-        <f>+I16/I9</f>
-        <v>0.31176048198386885</v>
+        <f>+I19/I18</f>
+        <v>0.28078406491576635</v>
       </c>
       <c r="J31" s="9">
-        <f>+J16/J9</f>
-        <v>0.21319000338185717</v>
-      </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="9" t="e">
-        <f t="shared" ref="L31:S31" si="24">+L16/L9</f>
+        <f>+J19/J18</f>
+        <v>7.3723578519410499E-2</v>
+      </c>
+      <c r="K31" s="9">
+        <f>+K19/K18</f>
+        <v>0.26923466069234664</v>
+      </c>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="9" t="e">
+        <f t="shared" ref="P31:W31" si="27">+P19/P18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M31" s="9" t="e">
-        <f t="shared" si="24"/>
+      <c r="Q31" s="9" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N31" s="9" t="e">
-        <f t="shared" si="24"/>
+      <c r="R31" s="9" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="9" t="e">
-        <f t="shared" si="24"/>
+      <c r="S31" s="9" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P31" s="9">
-        <f t="shared" si="24"/>
-        <v>0.29209636371097319</v>
-      </c>
-      <c r="Q31" s="9">
-        <f t="shared" si="24"/>
-        <v>0.17473428374748889</v>
-      </c>
-      <c r="R31" s="9">
-        <f t="shared" si="24"/>
-        <v>0.23332649928796623</v>
-      </c>
-      <c r="S31" s="9">
-        <f t="shared" si="24"/>
-        <v>0.26200839217918703</v>
-      </c>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
+      <c r="T31" s="9">
+        <f t="shared" si="27"/>
+        <v>0.25312145742523673</v>
+      </c>
+      <c r="U31" s="9">
+        <f t="shared" si="27"/>
+        <v>0.51174081691094186</v>
+      </c>
+      <c r="V31" s="9">
+        <f t="shared" si="27"/>
+        <v>0.34780891953897825</v>
+      </c>
+      <c r="W31" s="9">
+        <f t="shared" si="27"/>
+        <v>0.25884718498659509</v>
+      </c>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
@@ -3237,76 +3457,29 @@
       <c r="AS31" s="3"/>
       <c r="AT31" s="3"/>
       <c r="AU31" s="3"/>
-    </row>
-    <row r="32" spans="2:47" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="9">
-        <f t="shared" ref="C32:F32" si="25">+C19/C18</f>
-        <v>-13.904166666666551</v>
-      </c>
-      <c r="D32" s="9">
-        <f t="shared" si="25"/>
-        <v>0.31839196362321864</v>
-      </c>
-      <c r="E32" s="9">
-        <f t="shared" si="25"/>
-        <v>0.3266648631588438</v>
-      </c>
-      <c r="F32" s="9">
-        <f t="shared" si="25"/>
-        <v>0.32986772317720037</v>
-      </c>
-      <c r="G32" s="9">
-        <f>+G19/G18</f>
-        <v>0.48744013043921358</v>
-      </c>
-      <c r="H32" s="9">
-        <f>+H19/H18</f>
-        <v>0.29789394232888683</v>
-      </c>
-      <c r="I32" s="9">
-        <f>+I19/I18</f>
-        <v>0.28078406491576635</v>
-      </c>
-      <c r="J32" s="9">
-        <f>+J19/J18</f>
-        <v>7.3723578519410499E-2</v>
-      </c>
+      <c r="AV31" s="3"/>
+      <c r="AW31" s="3"/>
+      <c r="AX31" s="3"/>
+      <c r="AY31" s="3"/>
+    </row>
+    <row r="32" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
       <c r="K32" s="3"/>
-      <c r="L32" s="9" t="e">
-        <f t="shared" ref="L32:S32" si="26">+L19/L18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32" s="9" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N32" s="9" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O32" s="9" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P32" s="9">
-        <f t="shared" si="26"/>
-        <v>0.25312145742523673</v>
-      </c>
-      <c r="Q32" s="9">
-        <f t="shared" si="26"/>
-        <v>0.51174081691094186</v>
-      </c>
-      <c r="R32" s="9">
-        <f t="shared" si="26"/>
-        <v>0.34780891953897825</v>
-      </c>
-      <c r="S32" s="9">
-        <f t="shared" si="26"/>
-        <v>0.25884718498659509</v>
-      </c>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3335,8 +3508,12 @@
       <c r="AS32" s="3"/>
       <c r="AT32" s="3"/>
       <c r="AU32" s="3"/>
-    </row>
-    <row r="33" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV32" s="3"/>
+      <c r="AW32" s="3"/>
+      <c r="AX32" s="3"/>
+      <c r="AY32" s="3"/>
+    </row>
+    <row r="33" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -3382,8 +3559,12 @@
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3"/>
-    </row>
-    <row r="34" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV33" s="3"/>
+      <c r="AW33" s="3"/>
+      <c r="AX33" s="3"/>
+      <c r="AY33" s="3"/>
+    </row>
+    <row r="34" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -3429,8 +3610,12 @@
       <c r="AS34" s="3"/>
       <c r="AT34" s="3"/>
       <c r="AU34" s="3"/>
-    </row>
-    <row r="35" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV34" s="3"/>
+      <c r="AW34" s="3"/>
+      <c r="AX34" s="3"/>
+      <c r="AY34" s="3"/>
+    </row>
+    <row r="35" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -3476,8 +3661,12 @@
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
       <c r="AU35" s="3"/>
-    </row>
-    <row r="36" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV35" s="3"/>
+      <c r="AW35" s="3"/>
+      <c r="AX35" s="3"/>
+      <c r="AY35" s="3"/>
+    </row>
+    <row r="36" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -3523,8 +3712,12 @@
       <c r="AS36" s="3"/>
       <c r="AT36" s="3"/>
       <c r="AU36" s="3"/>
-    </row>
-    <row r="37" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV36" s="3"/>
+      <c r="AW36" s="3"/>
+      <c r="AX36" s="3"/>
+      <c r="AY36" s="3"/>
+    </row>
+    <row r="37" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -3570,8 +3763,12 @@
       <c r="AS37" s="3"/>
       <c r="AT37" s="3"/>
       <c r="AU37" s="3"/>
-    </row>
-    <row r="38" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV37" s="3"/>
+      <c r="AW37" s="3"/>
+      <c r="AX37" s="3"/>
+      <c r="AY37" s="3"/>
+    </row>
+    <row r="38" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -3617,8 +3814,12 @@
       <c r="AS38" s="3"/>
       <c r="AT38" s="3"/>
       <c r="AU38" s="3"/>
-    </row>
-    <row r="39" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV38" s="3"/>
+      <c r="AW38" s="3"/>
+      <c r="AX38" s="3"/>
+      <c r="AY38" s="3"/>
+    </row>
+    <row r="39" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -3664,8 +3865,12 @@
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
       <c r="AU39" s="3"/>
-    </row>
-    <row r="40" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV39" s="3"/>
+      <c r="AW39" s="3"/>
+      <c r="AX39" s="3"/>
+      <c r="AY39" s="3"/>
+    </row>
+    <row r="40" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -3711,8 +3916,12 @@
       <c r="AS40" s="3"/>
       <c r="AT40" s="3"/>
       <c r="AU40" s="3"/>
-    </row>
-    <row r="41" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV40" s="3"/>
+      <c r="AW40" s="3"/>
+      <c r="AX40" s="3"/>
+      <c r="AY40" s="3"/>
+    </row>
+    <row r="41" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3758,8 +3967,12 @@
       <c r="AS41" s="3"/>
       <c r="AT41" s="3"/>
       <c r="AU41" s="3"/>
-    </row>
-    <row r="42" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV41" s="3"/>
+      <c r="AW41" s="3"/>
+      <c r="AX41" s="3"/>
+      <c r="AY41" s="3"/>
+    </row>
+    <row r="42" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -3805,8 +4018,12 @@
       <c r="AS42" s="3"/>
       <c r="AT42" s="3"/>
       <c r="AU42" s="3"/>
-    </row>
-    <row r="43" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV42" s="3"/>
+      <c r="AW42" s="3"/>
+      <c r="AX42" s="3"/>
+      <c r="AY42" s="3"/>
+    </row>
+    <row r="43" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -3852,8 +4069,12 @@
       <c r="AS43" s="3"/>
       <c r="AT43" s="3"/>
       <c r="AU43" s="3"/>
-    </row>
-    <row r="44" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV43" s="3"/>
+      <c r="AW43" s="3"/>
+      <c r="AX43" s="3"/>
+      <c r="AY43" s="3"/>
+    </row>
+    <row r="44" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -3899,8 +4120,12 @@
       <c r="AS44" s="3"/>
       <c r="AT44" s="3"/>
       <c r="AU44" s="3"/>
-    </row>
-    <row r="45" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV44" s="3"/>
+      <c r="AW44" s="3"/>
+      <c r="AX44" s="3"/>
+      <c r="AY44" s="3"/>
+    </row>
+    <row r="45" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -3946,8 +4171,12 @@
       <c r="AS45" s="3"/>
       <c r="AT45" s="3"/>
       <c r="AU45" s="3"/>
-    </row>
-    <row r="46" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV45" s="3"/>
+      <c r="AW45" s="3"/>
+      <c r="AX45" s="3"/>
+      <c r="AY45" s="3"/>
+    </row>
+    <row r="46" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -3993,8 +4222,12 @@
       <c r="AS46" s="3"/>
       <c r="AT46" s="3"/>
       <c r="AU46" s="3"/>
-    </row>
-    <row r="47" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV46" s="3"/>
+      <c r="AW46" s="3"/>
+      <c r="AX46" s="3"/>
+      <c r="AY46" s="3"/>
+    </row>
+    <row r="47" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -4040,8 +4273,12 @@
       <c r="AS47" s="3"/>
       <c r="AT47" s="3"/>
       <c r="AU47" s="3"/>
-    </row>
-    <row r="48" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV47" s="3"/>
+      <c r="AW47" s="3"/>
+      <c r="AX47" s="3"/>
+      <c r="AY47" s="3"/>
+    </row>
+    <row r="48" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4087,8 +4324,12 @@
       <c r="AS48" s="3"/>
       <c r="AT48" s="3"/>
       <c r="AU48" s="3"/>
-    </row>
-    <row r="49" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV48" s="3"/>
+      <c r="AW48" s="3"/>
+      <c r="AX48" s="3"/>
+      <c r="AY48" s="3"/>
+    </row>
+    <row r="49" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -4134,8 +4375,12 @@
       <c r="AS49" s="3"/>
       <c r="AT49" s="3"/>
       <c r="AU49" s="3"/>
-    </row>
-    <row r="50" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV49" s="3"/>
+      <c r="AW49" s="3"/>
+      <c r="AX49" s="3"/>
+      <c r="AY49" s="3"/>
+    </row>
+    <row r="50" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -4181,8 +4426,12 @@
       <c r="AS50" s="3"/>
       <c r="AT50" s="3"/>
       <c r="AU50" s="3"/>
-    </row>
-    <row r="51" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV50" s="3"/>
+      <c r="AW50" s="3"/>
+      <c r="AX50" s="3"/>
+      <c r="AY50" s="3"/>
+    </row>
+    <row r="51" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -4228,8 +4477,12 @@
       <c r="AS51" s="3"/>
       <c r="AT51" s="3"/>
       <c r="AU51" s="3"/>
-    </row>
-    <row r="52" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV51" s="3"/>
+      <c r="AW51" s="3"/>
+      <c r="AX51" s="3"/>
+      <c r="AY51" s="3"/>
+    </row>
+    <row r="52" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -4275,8 +4528,12 @@
       <c r="AS52" s="3"/>
       <c r="AT52" s="3"/>
       <c r="AU52" s="3"/>
-    </row>
-    <row r="53" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV52" s="3"/>
+      <c r="AW52" s="3"/>
+      <c r="AX52" s="3"/>
+      <c r="AY52" s="3"/>
+    </row>
+    <row r="53" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -4322,8 +4579,12 @@
       <c r="AS53" s="3"/>
       <c r="AT53" s="3"/>
       <c r="AU53" s="3"/>
-    </row>
-    <row r="54" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV53" s="3"/>
+      <c r="AW53" s="3"/>
+      <c r="AX53" s="3"/>
+      <c r="AY53" s="3"/>
+    </row>
+    <row r="54" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -4369,8 +4630,12 @@
       <c r="AS54" s="3"/>
       <c r="AT54" s="3"/>
       <c r="AU54" s="3"/>
-    </row>
-    <row r="55" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV54" s="3"/>
+      <c r="AW54" s="3"/>
+      <c r="AX54" s="3"/>
+      <c r="AY54" s="3"/>
+    </row>
+    <row r="55" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -4416,8 +4681,12 @@
       <c r="AS55" s="3"/>
       <c r="AT55" s="3"/>
       <c r="AU55" s="3"/>
-    </row>
-    <row r="56" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV55" s="3"/>
+      <c r="AW55" s="3"/>
+      <c r="AX55" s="3"/>
+      <c r="AY55" s="3"/>
+    </row>
+    <row r="56" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -4463,8 +4732,12 @@
       <c r="AS56" s="3"/>
       <c r="AT56" s="3"/>
       <c r="AU56" s="3"/>
-    </row>
-    <row r="57" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV56" s="3"/>
+      <c r="AW56" s="3"/>
+      <c r="AX56" s="3"/>
+      <c r="AY56" s="3"/>
+    </row>
+    <row r="57" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -4510,8 +4783,12 @@
       <c r="AS57" s="3"/>
       <c r="AT57" s="3"/>
       <c r="AU57" s="3"/>
-    </row>
-    <row r="58" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV57" s="3"/>
+      <c r="AW57" s="3"/>
+      <c r="AX57" s="3"/>
+      <c r="AY57" s="3"/>
+    </row>
+    <row r="58" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -4557,8 +4834,12 @@
       <c r="AS58" s="3"/>
       <c r="AT58" s="3"/>
       <c r="AU58" s="3"/>
-    </row>
-    <row r="59" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV58" s="3"/>
+      <c r="AW58" s="3"/>
+      <c r="AX58" s="3"/>
+      <c r="AY58" s="3"/>
+    </row>
+    <row r="59" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -4604,8 +4885,12 @@
       <c r="AS59" s="3"/>
       <c r="AT59" s="3"/>
       <c r="AU59" s="3"/>
-    </row>
-    <row r="60" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV59" s="3"/>
+      <c r="AW59" s="3"/>
+      <c r="AX59" s="3"/>
+      <c r="AY59" s="3"/>
+    </row>
+    <row r="60" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -4651,8 +4936,12 @@
       <c r="AS60" s="3"/>
       <c r="AT60" s="3"/>
       <c r="AU60" s="3"/>
-    </row>
-    <row r="61" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV60" s="3"/>
+      <c r="AW60" s="3"/>
+      <c r="AX60" s="3"/>
+      <c r="AY60" s="3"/>
+    </row>
+    <row r="61" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -4698,8 +4987,12 @@
       <c r="AS61" s="3"/>
       <c r="AT61" s="3"/>
       <c r="AU61" s="3"/>
-    </row>
-    <row r="62" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV61" s="3"/>
+      <c r="AW61" s="3"/>
+      <c r="AX61" s="3"/>
+      <c r="AY61" s="3"/>
+    </row>
+    <row r="62" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -4745,8 +5038,12 @@
       <c r="AS62" s="3"/>
       <c r="AT62" s="3"/>
       <c r="AU62" s="3"/>
-    </row>
-    <row r="63" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV62" s="3"/>
+      <c r="AW62" s="3"/>
+      <c r="AX62" s="3"/>
+      <c r="AY62" s="3"/>
+    </row>
+    <row r="63" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -4792,8 +5089,12 @@
       <c r="AS63" s="3"/>
       <c r="AT63" s="3"/>
       <c r="AU63" s="3"/>
-    </row>
-    <row r="64" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV63" s="3"/>
+      <c r="AW63" s="3"/>
+      <c r="AX63" s="3"/>
+      <c r="AY63" s="3"/>
+    </row>
+    <row r="64" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -4839,8 +5140,12 @@
       <c r="AS64" s="3"/>
       <c r="AT64" s="3"/>
       <c r="AU64" s="3"/>
-    </row>
-    <row r="65" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV64" s="3"/>
+      <c r="AW64" s="3"/>
+      <c r="AX64" s="3"/>
+      <c r="AY64" s="3"/>
+    </row>
+    <row r="65" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -4886,8 +5191,12 @@
       <c r="AS65" s="3"/>
       <c r="AT65" s="3"/>
       <c r="AU65" s="3"/>
-    </row>
-    <row r="66" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV65" s="3"/>
+      <c r="AW65" s="3"/>
+      <c r="AX65" s="3"/>
+      <c r="AY65" s="3"/>
+    </row>
+    <row r="66" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -4933,8 +5242,12 @@
       <c r="AS66" s="3"/>
       <c r="AT66" s="3"/>
       <c r="AU66" s="3"/>
-    </row>
-    <row r="67" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV66" s="3"/>
+      <c r="AW66" s="3"/>
+      <c r="AX66" s="3"/>
+      <c r="AY66" s="3"/>
+    </row>
+    <row r="67" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -4980,8 +5293,12 @@
       <c r="AS67" s="3"/>
       <c r="AT67" s="3"/>
       <c r="AU67" s="3"/>
-    </row>
-    <row r="68" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV67" s="3"/>
+      <c r="AW67" s="3"/>
+      <c r="AX67" s="3"/>
+      <c r="AY67" s="3"/>
+    </row>
+    <row r="68" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -5027,8 +5344,12 @@
       <c r="AS68" s="3"/>
       <c r="AT68" s="3"/>
       <c r="AU68" s="3"/>
-    </row>
-    <row r="69" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV68" s="3"/>
+      <c r="AW68" s="3"/>
+      <c r="AX68" s="3"/>
+      <c r="AY68" s="3"/>
+    </row>
+    <row r="69" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -5074,8 +5395,12 @@
       <c r="AS69" s="3"/>
       <c r="AT69" s="3"/>
       <c r="AU69" s="3"/>
-    </row>
-    <row r="70" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV69" s="3"/>
+      <c r="AW69" s="3"/>
+      <c r="AX69" s="3"/>
+      <c r="AY69" s="3"/>
+    </row>
+    <row r="70" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -5121,8 +5446,12 @@
       <c r="AS70" s="3"/>
       <c r="AT70" s="3"/>
       <c r="AU70" s="3"/>
-    </row>
-    <row r="71" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV70" s="3"/>
+      <c r="AW70" s="3"/>
+      <c r="AX70" s="3"/>
+      <c r="AY70" s="3"/>
+    </row>
+    <row r="71" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -5168,8 +5497,12 @@
       <c r="AS71" s="3"/>
       <c r="AT71" s="3"/>
       <c r="AU71" s="3"/>
-    </row>
-    <row r="72" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV71" s="3"/>
+      <c r="AW71" s="3"/>
+      <c r="AX71" s="3"/>
+      <c r="AY71" s="3"/>
+    </row>
+    <row r="72" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -5215,8 +5548,12 @@
       <c r="AS72" s="3"/>
       <c r="AT72" s="3"/>
       <c r="AU72" s="3"/>
-    </row>
-    <row r="73" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV72" s="3"/>
+      <c r="AW72" s="3"/>
+      <c r="AX72" s="3"/>
+      <c r="AY72" s="3"/>
+    </row>
+    <row r="73" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -5262,8 +5599,12 @@
       <c r="AS73" s="3"/>
       <c r="AT73" s="3"/>
       <c r="AU73" s="3"/>
-    </row>
-    <row r="74" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV73" s="3"/>
+      <c r="AW73" s="3"/>
+      <c r="AX73" s="3"/>
+      <c r="AY73" s="3"/>
+    </row>
+    <row r="74" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -5309,8 +5650,12 @@
       <c r="AS74" s="3"/>
       <c r="AT74" s="3"/>
       <c r="AU74" s="3"/>
-    </row>
-    <row r="75" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV74" s="3"/>
+      <c r="AW74" s="3"/>
+      <c r="AX74" s="3"/>
+      <c r="AY74" s="3"/>
+    </row>
+    <row r="75" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -5356,8 +5701,12 @@
       <c r="AS75" s="3"/>
       <c r="AT75" s="3"/>
       <c r="AU75" s="3"/>
-    </row>
-    <row r="76" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV75" s="3"/>
+      <c r="AW75" s="3"/>
+      <c r="AX75" s="3"/>
+      <c r="AY75" s="3"/>
+    </row>
+    <row r="76" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -5403,8 +5752,12 @@
       <c r="AS76" s="3"/>
       <c r="AT76" s="3"/>
       <c r="AU76" s="3"/>
-    </row>
-    <row r="77" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV76" s="3"/>
+      <c r="AW76" s="3"/>
+      <c r="AX76" s="3"/>
+      <c r="AY76" s="3"/>
+    </row>
+    <row r="77" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -5450,8 +5803,12 @@
       <c r="AS77" s="3"/>
       <c r="AT77" s="3"/>
       <c r="AU77" s="3"/>
-    </row>
-    <row r="78" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV77" s="3"/>
+      <c r="AW77" s="3"/>
+      <c r="AX77" s="3"/>
+      <c r="AY77" s="3"/>
+    </row>
+    <row r="78" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -5497,8 +5854,12 @@
       <c r="AS78" s="3"/>
       <c r="AT78" s="3"/>
       <c r="AU78" s="3"/>
-    </row>
-    <row r="79" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV78" s="3"/>
+      <c r="AW78" s="3"/>
+      <c r="AX78" s="3"/>
+      <c r="AY78" s="3"/>
+    </row>
+    <row r="79" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -5544,8 +5905,12 @@
       <c r="AS79" s="3"/>
       <c r="AT79" s="3"/>
       <c r="AU79" s="3"/>
-    </row>
-    <row r="80" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV79" s="3"/>
+      <c r="AW79" s="3"/>
+      <c r="AX79" s="3"/>
+      <c r="AY79" s="3"/>
+    </row>
+    <row r="80" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -5591,8 +5956,12 @@
       <c r="AS80" s="3"/>
       <c r="AT80" s="3"/>
       <c r="AU80" s="3"/>
-    </row>
-    <row r="81" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV80" s="3"/>
+      <c r="AW80" s="3"/>
+      <c r="AX80" s="3"/>
+      <c r="AY80" s="3"/>
+    </row>
+    <row r="81" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -5638,8 +6007,12 @@
       <c r="AS81" s="3"/>
       <c r="AT81" s="3"/>
       <c r="AU81" s="3"/>
-    </row>
-    <row r="82" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV81" s="3"/>
+      <c r="AW81" s="3"/>
+      <c r="AX81" s="3"/>
+      <c r="AY81" s="3"/>
+    </row>
+    <row r="82" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -5685,8 +6058,12 @@
       <c r="AS82" s="3"/>
       <c r="AT82" s="3"/>
       <c r="AU82" s="3"/>
-    </row>
-    <row r="83" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV82" s="3"/>
+      <c r="AW82" s="3"/>
+      <c r="AX82" s="3"/>
+      <c r="AY82" s="3"/>
+    </row>
+    <row r="83" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -5732,8 +6109,12 @@
       <c r="AS83" s="3"/>
       <c r="AT83" s="3"/>
       <c r="AU83" s="3"/>
-    </row>
-    <row r="84" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV83" s="3"/>
+      <c r="AW83" s="3"/>
+      <c r="AX83" s="3"/>
+      <c r="AY83" s="3"/>
+    </row>
+    <row r="84" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -5779,8 +6160,12 @@
       <c r="AS84" s="3"/>
       <c r="AT84" s="3"/>
       <c r="AU84" s="3"/>
-    </row>
-    <row r="85" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV84" s="3"/>
+      <c r="AW84" s="3"/>
+      <c r="AX84" s="3"/>
+      <c r="AY84" s="3"/>
+    </row>
+    <row r="85" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -5826,8 +6211,12 @@
       <c r="AS85" s="3"/>
       <c r="AT85" s="3"/>
       <c r="AU85" s="3"/>
-    </row>
-    <row r="86" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV85" s="3"/>
+      <c r="AW85" s="3"/>
+      <c r="AX85" s="3"/>
+      <c r="AY85" s="3"/>
+    </row>
+    <row r="86" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -5873,8 +6262,12 @@
       <c r="AS86" s="3"/>
       <c r="AT86" s="3"/>
       <c r="AU86" s="3"/>
-    </row>
-    <row r="87" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV86" s="3"/>
+      <c r="AW86" s="3"/>
+      <c r="AX86" s="3"/>
+      <c r="AY86" s="3"/>
+    </row>
+    <row r="87" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -5920,8 +6313,12 @@
       <c r="AS87" s="3"/>
       <c r="AT87" s="3"/>
       <c r="AU87" s="3"/>
-    </row>
-    <row r="88" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV87" s="3"/>
+      <c r="AW87" s="3"/>
+      <c r="AX87" s="3"/>
+      <c r="AY87" s="3"/>
+    </row>
+    <row r="88" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -5967,8 +6364,12 @@
       <c r="AS88" s="3"/>
       <c r="AT88" s="3"/>
       <c r="AU88" s="3"/>
-    </row>
-    <row r="89" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV88" s="3"/>
+      <c r="AW88" s="3"/>
+      <c r="AX88" s="3"/>
+      <c r="AY88" s="3"/>
+    </row>
+    <row r="89" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -6014,8 +6415,12 @@
       <c r="AS89" s="3"/>
       <c r="AT89" s="3"/>
       <c r="AU89" s="3"/>
-    </row>
-    <row r="90" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV89" s="3"/>
+      <c r="AW89" s="3"/>
+      <c r="AX89" s="3"/>
+      <c r="AY89" s="3"/>
+    </row>
+    <row r="90" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -6061,8 +6466,12 @@
       <c r="AS90" s="3"/>
       <c r="AT90" s="3"/>
       <c r="AU90" s="3"/>
-    </row>
-    <row r="91" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV90" s="3"/>
+      <c r="AW90" s="3"/>
+      <c r="AX90" s="3"/>
+      <c r="AY90" s="3"/>
+    </row>
+    <row r="91" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -6108,8 +6517,12 @@
       <c r="AS91" s="3"/>
       <c r="AT91" s="3"/>
       <c r="AU91" s="3"/>
-    </row>
-    <row r="92" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV91" s="3"/>
+      <c r="AW91" s="3"/>
+      <c r="AX91" s="3"/>
+      <c r="AY91" s="3"/>
+    </row>
+    <row r="92" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -6155,8 +6568,12 @@
       <c r="AS92" s="3"/>
       <c r="AT92" s="3"/>
       <c r="AU92" s="3"/>
-    </row>
-    <row r="93" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV92" s="3"/>
+      <c r="AW92" s="3"/>
+      <c r="AX92" s="3"/>
+      <c r="AY92" s="3"/>
+    </row>
+    <row r="93" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -6202,8 +6619,12 @@
       <c r="AS93" s="3"/>
       <c r="AT93" s="3"/>
       <c r="AU93" s="3"/>
-    </row>
-    <row r="94" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV93" s="3"/>
+      <c r="AW93" s="3"/>
+      <c r="AX93" s="3"/>
+      <c r="AY93" s="3"/>
+    </row>
+    <row r="94" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -6249,8 +6670,12 @@
       <c r="AS94" s="3"/>
       <c r="AT94" s="3"/>
       <c r="AU94" s="3"/>
-    </row>
-    <row r="95" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV94" s="3"/>
+      <c r="AW94" s="3"/>
+      <c r="AX94" s="3"/>
+      <c r="AY94" s="3"/>
+    </row>
+    <row r="95" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -6296,8 +6721,12 @@
       <c r="AS95" s="3"/>
       <c r="AT95" s="3"/>
       <c r="AU95" s="3"/>
-    </row>
-    <row r="96" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV95" s="3"/>
+      <c r="AW95" s="3"/>
+      <c r="AX95" s="3"/>
+      <c r="AY95" s="3"/>
+    </row>
+    <row r="96" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -6343,8 +6772,12 @@
       <c r="AS96" s="3"/>
       <c r="AT96" s="3"/>
       <c r="AU96" s="3"/>
-    </row>
-    <row r="97" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV96" s="3"/>
+      <c r="AW96" s="3"/>
+      <c r="AX96" s="3"/>
+      <c r="AY96" s="3"/>
+    </row>
+    <row r="97" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -6390,8 +6823,12 @@
       <c r="AS97" s="3"/>
       <c r="AT97" s="3"/>
       <c r="AU97" s="3"/>
-    </row>
-    <row r="98" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV97" s="3"/>
+      <c r="AW97" s="3"/>
+      <c r="AX97" s="3"/>
+      <c r="AY97" s="3"/>
+    </row>
+    <row r="98" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -6437,8 +6874,12 @@
       <c r="AS98" s="3"/>
       <c r="AT98" s="3"/>
       <c r="AU98" s="3"/>
-    </row>
-    <row r="99" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV98" s="3"/>
+      <c r="AW98" s="3"/>
+      <c r="AX98" s="3"/>
+      <c r="AY98" s="3"/>
+    </row>
+    <row r="99" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -6484,8 +6925,12 @@
       <c r="AS99" s="3"/>
       <c r="AT99" s="3"/>
       <c r="AU99" s="3"/>
-    </row>
-    <row r="100" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV99" s="3"/>
+      <c r="AW99" s="3"/>
+      <c r="AX99" s="3"/>
+      <c r="AY99" s="3"/>
+    </row>
+    <row r="100" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -6531,8 +6976,12 @@
       <c r="AS100" s="3"/>
       <c r="AT100" s="3"/>
       <c r="AU100" s="3"/>
-    </row>
-    <row r="101" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV100" s="3"/>
+      <c r="AW100" s="3"/>
+      <c r="AX100" s="3"/>
+      <c r="AY100" s="3"/>
+    </row>
+    <row r="101" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -6578,8 +7027,12 @@
       <c r="AS101" s="3"/>
       <c r="AT101" s="3"/>
       <c r="AU101" s="3"/>
-    </row>
-    <row r="102" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV101" s="3"/>
+      <c r="AW101" s="3"/>
+      <c r="AX101" s="3"/>
+      <c r="AY101" s="3"/>
+    </row>
+    <row r="102" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -6625,8 +7078,12 @@
       <c r="AS102" s="3"/>
       <c r="AT102" s="3"/>
       <c r="AU102" s="3"/>
-    </row>
-    <row r="103" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV102" s="3"/>
+      <c r="AW102" s="3"/>
+      <c r="AX102" s="3"/>
+      <c r="AY102" s="3"/>
+    </row>
+    <row r="103" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -6672,8 +7129,12 @@
       <c r="AS103" s="3"/>
       <c r="AT103" s="3"/>
       <c r="AU103" s="3"/>
-    </row>
-    <row r="104" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV103" s="3"/>
+      <c r="AW103" s="3"/>
+      <c r="AX103" s="3"/>
+      <c r="AY103" s="3"/>
+    </row>
+    <row r="104" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -6719,8 +7180,12 @@
       <c r="AS104" s="3"/>
       <c r="AT104" s="3"/>
       <c r="AU104" s="3"/>
-    </row>
-    <row r="105" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV104" s="3"/>
+      <c r="AW104" s="3"/>
+      <c r="AX104" s="3"/>
+      <c r="AY104" s="3"/>
+    </row>
+    <row r="105" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -6766,8 +7231,12 @@
       <c r="AS105" s="3"/>
       <c r="AT105" s="3"/>
       <c r="AU105" s="3"/>
-    </row>
-    <row r="106" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV105" s="3"/>
+      <c r="AW105" s="3"/>
+      <c r="AX105" s="3"/>
+      <c r="AY105" s="3"/>
+    </row>
+    <row r="106" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -6813,8 +7282,12 @@
       <c r="AS106" s="3"/>
       <c r="AT106" s="3"/>
       <c r="AU106" s="3"/>
-    </row>
-    <row r="107" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV106" s="3"/>
+      <c r="AW106" s="3"/>
+      <c r="AX106" s="3"/>
+      <c r="AY106" s="3"/>
+    </row>
+    <row r="107" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -6860,8 +7333,12 @@
       <c r="AS107" s="3"/>
       <c r="AT107" s="3"/>
       <c r="AU107" s="3"/>
-    </row>
-    <row r="108" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV107" s="3"/>
+      <c r="AW107" s="3"/>
+      <c r="AX107" s="3"/>
+      <c r="AY107" s="3"/>
+    </row>
+    <row r="108" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -6907,8 +7384,12 @@
       <c r="AS108" s="3"/>
       <c r="AT108" s="3"/>
       <c r="AU108" s="3"/>
-    </row>
-    <row r="109" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV108" s="3"/>
+      <c r="AW108" s="3"/>
+      <c r="AX108" s="3"/>
+      <c r="AY108" s="3"/>
+    </row>
+    <row r="109" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -6954,8 +7435,12 @@
       <c r="AS109" s="3"/>
       <c r="AT109" s="3"/>
       <c r="AU109" s="3"/>
-    </row>
-    <row r="110" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV109" s="3"/>
+      <c r="AW109" s="3"/>
+      <c r="AX109" s="3"/>
+      <c r="AY109" s="3"/>
+    </row>
+    <row r="110" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -7001,8 +7486,12 @@
       <c r="AS110" s="3"/>
       <c r="AT110" s="3"/>
       <c r="AU110" s="3"/>
-    </row>
-    <row r="111" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV110" s="3"/>
+      <c r="AW110" s="3"/>
+      <c r="AX110" s="3"/>
+      <c r="AY110" s="3"/>
+    </row>
+    <row r="111" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -7048,8 +7537,12 @@
       <c r="AS111" s="3"/>
       <c r="AT111" s="3"/>
       <c r="AU111" s="3"/>
-    </row>
-    <row r="112" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV111" s="3"/>
+      <c r="AW111" s="3"/>
+      <c r="AX111" s="3"/>
+      <c r="AY111" s="3"/>
+    </row>
+    <row r="112" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -7095,8 +7588,12 @@
       <c r="AS112" s="3"/>
       <c r="AT112" s="3"/>
       <c r="AU112" s="3"/>
-    </row>
-    <row r="113" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV112" s="3"/>
+      <c r="AW112" s="3"/>
+      <c r="AX112" s="3"/>
+      <c r="AY112" s="3"/>
+    </row>
+    <row r="113" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -7142,8 +7639,12 @@
       <c r="AS113" s="3"/>
       <c r="AT113" s="3"/>
       <c r="AU113" s="3"/>
-    </row>
-    <row r="114" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV113" s="3"/>
+      <c r="AW113" s="3"/>
+      <c r="AX113" s="3"/>
+      <c r="AY113" s="3"/>
+    </row>
+    <row r="114" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -7189,8 +7690,12 @@
       <c r="AS114" s="3"/>
       <c r="AT114" s="3"/>
       <c r="AU114" s="3"/>
-    </row>
-    <row r="115" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV114" s="3"/>
+      <c r="AW114" s="3"/>
+      <c r="AX114" s="3"/>
+      <c r="AY114" s="3"/>
+    </row>
+    <row r="115" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -7236,8 +7741,12 @@
       <c r="AS115" s="3"/>
       <c r="AT115" s="3"/>
       <c r="AU115" s="3"/>
-    </row>
-    <row r="116" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV115" s="3"/>
+      <c r="AW115" s="3"/>
+      <c r="AX115" s="3"/>
+      <c r="AY115" s="3"/>
+    </row>
+    <row r="116" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -7283,8 +7792,12 @@
       <c r="AS116" s="3"/>
       <c r="AT116" s="3"/>
       <c r="AU116" s="3"/>
-    </row>
-    <row r="117" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV116" s="3"/>
+      <c r="AW116" s="3"/>
+      <c r="AX116" s="3"/>
+      <c r="AY116" s="3"/>
+    </row>
+    <row r="117" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -7330,8 +7843,12 @@
       <c r="AS117" s="3"/>
       <c r="AT117" s="3"/>
       <c r="AU117" s="3"/>
-    </row>
-    <row r="118" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV117" s="3"/>
+      <c r="AW117" s="3"/>
+      <c r="AX117" s="3"/>
+      <c r="AY117" s="3"/>
+    </row>
+    <row r="118" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -7377,8 +7894,12 @@
       <c r="AS118" s="3"/>
       <c r="AT118" s="3"/>
       <c r="AU118" s="3"/>
-    </row>
-    <row r="119" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV118" s="3"/>
+      <c r="AW118" s="3"/>
+      <c r="AX118" s="3"/>
+      <c r="AY118" s="3"/>
+    </row>
+    <row r="119" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -7424,8 +7945,12 @@
       <c r="AS119" s="3"/>
       <c r="AT119" s="3"/>
       <c r="AU119" s="3"/>
-    </row>
-    <row r="120" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV119" s="3"/>
+      <c r="AW119" s="3"/>
+      <c r="AX119" s="3"/>
+      <c r="AY119" s="3"/>
+    </row>
+    <row r="120" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -7471,8 +7996,12 @@
       <c r="AS120" s="3"/>
       <c r="AT120" s="3"/>
       <c r="AU120" s="3"/>
-    </row>
-    <row r="121" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV120" s="3"/>
+      <c r="AW120" s="3"/>
+      <c r="AX120" s="3"/>
+      <c r="AY120" s="3"/>
+    </row>
+    <row r="121" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -7518,8 +8047,12 @@
       <c r="AS121" s="3"/>
       <c r="AT121" s="3"/>
       <c r="AU121" s="3"/>
-    </row>
-    <row r="122" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV121" s="3"/>
+      <c r="AW121" s="3"/>
+      <c r="AX121" s="3"/>
+      <c r="AY121" s="3"/>
+    </row>
+    <row r="122" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -7565,8 +8098,12 @@
       <c r="AS122" s="3"/>
       <c r="AT122" s="3"/>
       <c r="AU122" s="3"/>
-    </row>
-    <row r="123" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV122" s="3"/>
+      <c r="AW122" s="3"/>
+      <c r="AX122" s="3"/>
+      <c r="AY122" s="3"/>
+    </row>
+    <row r="123" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -7612,8 +8149,12 @@
       <c r="AS123" s="3"/>
       <c r="AT123" s="3"/>
       <c r="AU123" s="3"/>
-    </row>
-    <row r="124" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV123" s="3"/>
+      <c r="AW123" s="3"/>
+      <c r="AX123" s="3"/>
+      <c r="AY123" s="3"/>
+    </row>
+    <row r="124" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -7659,8 +8200,12 @@
       <c r="AS124" s="3"/>
       <c r="AT124" s="3"/>
       <c r="AU124" s="3"/>
-    </row>
-    <row r="125" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV124" s="3"/>
+      <c r="AW124" s="3"/>
+      <c r="AX124" s="3"/>
+      <c r="AY124" s="3"/>
+    </row>
+    <row r="125" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -7706,8 +8251,12 @@
       <c r="AS125" s="3"/>
       <c r="AT125" s="3"/>
       <c r="AU125" s="3"/>
-    </row>
-    <row r="126" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV125" s="3"/>
+      <c r="AW125" s="3"/>
+      <c r="AX125" s="3"/>
+      <c r="AY125" s="3"/>
+    </row>
+    <row r="126" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -7753,8 +8302,12 @@
       <c r="AS126" s="3"/>
       <c r="AT126" s="3"/>
       <c r="AU126" s="3"/>
-    </row>
-    <row r="127" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV126" s="3"/>
+      <c r="AW126" s="3"/>
+      <c r="AX126" s="3"/>
+      <c r="AY126" s="3"/>
+    </row>
+    <row r="127" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -7800,8 +8353,12 @@
       <c r="AS127" s="3"/>
       <c r="AT127" s="3"/>
       <c r="AU127" s="3"/>
-    </row>
-    <row r="128" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV127" s="3"/>
+      <c r="AW127" s="3"/>
+      <c r="AX127" s="3"/>
+      <c r="AY127" s="3"/>
+    </row>
+    <row r="128" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -7847,8 +8404,12 @@
       <c r="AS128" s="3"/>
       <c r="AT128" s="3"/>
       <c r="AU128" s="3"/>
-    </row>
-    <row r="129" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV128" s="3"/>
+      <c r="AW128" s="3"/>
+      <c r="AX128" s="3"/>
+      <c r="AY128" s="3"/>
+    </row>
+    <row r="129" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -7894,8 +8455,12 @@
       <c r="AS129" s="3"/>
       <c r="AT129" s="3"/>
       <c r="AU129" s="3"/>
-    </row>
-    <row r="130" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV129" s="3"/>
+      <c r="AW129" s="3"/>
+      <c r="AX129" s="3"/>
+      <c r="AY129" s="3"/>
+    </row>
+    <row r="130" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -7941,8 +8506,12 @@
       <c r="AS130" s="3"/>
       <c r="AT130" s="3"/>
       <c r="AU130" s="3"/>
-    </row>
-    <row r="131" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV130" s="3"/>
+      <c r="AW130" s="3"/>
+      <c r="AX130" s="3"/>
+      <c r="AY130" s="3"/>
+    </row>
+    <row r="131" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -7988,8 +8557,12 @@
       <c r="AS131" s="3"/>
       <c r="AT131" s="3"/>
       <c r="AU131" s="3"/>
-    </row>
-    <row r="132" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV131" s="3"/>
+      <c r="AW131" s="3"/>
+      <c r="AX131" s="3"/>
+      <c r="AY131" s="3"/>
+    </row>
+    <row r="132" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -8035,8 +8608,12 @@
       <c r="AS132" s="3"/>
       <c r="AT132" s="3"/>
       <c r="AU132" s="3"/>
-    </row>
-    <row r="133" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV132" s="3"/>
+      <c r="AW132" s="3"/>
+      <c r="AX132" s="3"/>
+      <c r="AY132" s="3"/>
+    </row>
+    <row r="133" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -8082,8 +8659,12 @@
       <c r="AS133" s="3"/>
       <c r="AT133" s="3"/>
       <c r="AU133" s="3"/>
-    </row>
-    <row r="134" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV133" s="3"/>
+      <c r="AW133" s="3"/>
+      <c r="AX133" s="3"/>
+      <c r="AY133" s="3"/>
+    </row>
+    <row r="134" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -8129,8 +8710,12 @@
       <c r="AS134" s="3"/>
       <c r="AT134" s="3"/>
       <c r="AU134" s="3"/>
-    </row>
-    <row r="135" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV134" s="3"/>
+      <c r="AW134" s="3"/>
+      <c r="AX134" s="3"/>
+      <c r="AY134" s="3"/>
+    </row>
+    <row r="135" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -8176,8 +8761,12 @@
       <c r="AS135" s="3"/>
       <c r="AT135" s="3"/>
       <c r="AU135" s="3"/>
-    </row>
-    <row r="136" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV135" s="3"/>
+      <c r="AW135" s="3"/>
+      <c r="AX135" s="3"/>
+      <c r="AY135" s="3"/>
+    </row>
+    <row r="136" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -8223,8 +8812,12 @@
       <c r="AS136" s="3"/>
       <c r="AT136" s="3"/>
       <c r="AU136" s="3"/>
-    </row>
-    <row r="137" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV136" s="3"/>
+      <c r="AW136" s="3"/>
+      <c r="AX136" s="3"/>
+      <c r="AY136" s="3"/>
+    </row>
+    <row r="137" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -8270,8 +8863,12 @@
       <c r="AS137" s="3"/>
       <c r="AT137" s="3"/>
       <c r="AU137" s="3"/>
-    </row>
-    <row r="138" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV137" s="3"/>
+      <c r="AW137" s="3"/>
+      <c r="AX137" s="3"/>
+      <c r="AY137" s="3"/>
+    </row>
+    <row r="138" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -8317,8 +8914,12 @@
       <c r="AS138" s="3"/>
       <c r="AT138" s="3"/>
       <c r="AU138" s="3"/>
-    </row>
-    <row r="139" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV138" s="3"/>
+      <c r="AW138" s="3"/>
+      <c r="AX138" s="3"/>
+      <c r="AY138" s="3"/>
+    </row>
+    <row r="139" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -8364,8 +8965,12 @@
       <c r="AS139" s="3"/>
       <c r="AT139" s="3"/>
       <c r="AU139" s="3"/>
-    </row>
-    <row r="140" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV139" s="3"/>
+      <c r="AW139" s="3"/>
+      <c r="AX139" s="3"/>
+      <c r="AY139" s="3"/>
+    </row>
+    <row r="140" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -8411,8 +9016,12 @@
       <c r="AS140" s="3"/>
       <c r="AT140" s="3"/>
       <c r="AU140" s="3"/>
-    </row>
-    <row r="141" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV140" s="3"/>
+      <c r="AW140" s="3"/>
+      <c r="AX140" s="3"/>
+      <c r="AY140" s="3"/>
+    </row>
+    <row r="141" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -8458,8 +9067,12 @@
       <c r="AS141" s="3"/>
       <c r="AT141" s="3"/>
       <c r="AU141" s="3"/>
-    </row>
-    <row r="142" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV141" s="3"/>
+      <c r="AW141" s="3"/>
+      <c r="AX141" s="3"/>
+      <c r="AY141" s="3"/>
+    </row>
+    <row r="142" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -8505,8 +9118,12 @@
       <c r="AS142" s="3"/>
       <c r="AT142" s="3"/>
       <c r="AU142" s="3"/>
-    </row>
-    <row r="143" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV142" s="3"/>
+      <c r="AW142" s="3"/>
+      <c r="AX142" s="3"/>
+      <c r="AY142" s="3"/>
+    </row>
+    <row r="143" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -8552,8 +9169,12 @@
       <c r="AS143" s="3"/>
       <c r="AT143" s="3"/>
       <c r="AU143" s="3"/>
-    </row>
-    <row r="144" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV143" s="3"/>
+      <c r="AW143" s="3"/>
+      <c r="AX143" s="3"/>
+      <c r="AY143" s="3"/>
+    </row>
+    <row r="144" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -8599,8 +9220,12 @@
       <c r="AS144" s="3"/>
       <c r="AT144" s="3"/>
       <c r="AU144" s="3"/>
-    </row>
-    <row r="145" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV144" s="3"/>
+      <c r="AW144" s="3"/>
+      <c r="AX144" s="3"/>
+      <c r="AY144" s="3"/>
+    </row>
+    <row r="145" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -8646,8 +9271,12 @@
       <c r="AS145" s="3"/>
       <c r="AT145" s="3"/>
       <c r="AU145" s="3"/>
-    </row>
-    <row r="146" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV145" s="3"/>
+      <c r="AW145" s="3"/>
+      <c r="AX145" s="3"/>
+      <c r="AY145" s="3"/>
+    </row>
+    <row r="146" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -8693,8 +9322,12 @@
       <c r="AS146" s="3"/>
       <c r="AT146" s="3"/>
       <c r="AU146" s="3"/>
-    </row>
-    <row r="147" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV146" s="3"/>
+      <c r="AW146" s="3"/>
+      <c r="AX146" s="3"/>
+      <c r="AY146" s="3"/>
+    </row>
+    <row r="147" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -8740,8 +9373,12 @@
       <c r="AS147" s="3"/>
       <c r="AT147" s="3"/>
       <c r="AU147" s="3"/>
-    </row>
-    <row r="148" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV147" s="3"/>
+      <c r="AW147" s="3"/>
+      <c r="AX147" s="3"/>
+      <c r="AY147" s="3"/>
+    </row>
+    <row r="148" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -8787,8 +9424,12 @@
       <c r="AS148" s="3"/>
       <c r="AT148" s="3"/>
       <c r="AU148" s="3"/>
-    </row>
-    <row r="149" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV148" s="3"/>
+      <c r="AW148" s="3"/>
+      <c r="AX148" s="3"/>
+      <c r="AY148" s="3"/>
+    </row>
+    <row r="149" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -8834,8 +9475,12 @@
       <c r="AS149" s="3"/>
       <c r="AT149" s="3"/>
       <c r="AU149" s="3"/>
-    </row>
-    <row r="150" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV149" s="3"/>
+      <c r="AW149" s="3"/>
+      <c r="AX149" s="3"/>
+      <c r="AY149" s="3"/>
+    </row>
+    <row r="150" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -8881,8 +9526,12 @@
       <c r="AS150" s="3"/>
       <c r="AT150" s="3"/>
       <c r="AU150" s="3"/>
-    </row>
-    <row r="151" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV150" s="3"/>
+      <c r="AW150" s="3"/>
+      <c r="AX150" s="3"/>
+      <c r="AY150" s="3"/>
+    </row>
+    <row r="151" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -8928,8 +9577,12 @@
       <c r="AS151" s="3"/>
       <c r="AT151" s="3"/>
       <c r="AU151" s="3"/>
-    </row>
-    <row r="152" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV151" s="3"/>
+      <c r="AW151" s="3"/>
+      <c r="AX151" s="3"/>
+      <c r="AY151" s="3"/>
+    </row>
+    <row r="152" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -8975,8 +9628,12 @@
       <c r="AS152" s="3"/>
       <c r="AT152" s="3"/>
       <c r="AU152" s="3"/>
-    </row>
-    <row r="153" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV152" s="3"/>
+      <c r="AW152" s="3"/>
+      <c r="AX152" s="3"/>
+      <c r="AY152" s="3"/>
+    </row>
+    <row r="153" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -9022,8 +9679,12 @@
       <c r="AS153" s="3"/>
       <c r="AT153" s="3"/>
       <c r="AU153" s="3"/>
-    </row>
-    <row r="154" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV153" s="3"/>
+      <c r="AW153" s="3"/>
+      <c r="AX153" s="3"/>
+      <c r="AY153" s="3"/>
+    </row>
+    <row r="154" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -9069,8 +9730,12 @@
       <c r="AS154" s="3"/>
       <c r="AT154" s="3"/>
       <c r="AU154" s="3"/>
-    </row>
-    <row r="155" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV154" s="3"/>
+      <c r="AW154" s="3"/>
+      <c r="AX154" s="3"/>
+      <c r="AY154" s="3"/>
+    </row>
+    <row r="155" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -9116,8 +9781,12 @@
       <c r="AS155" s="3"/>
       <c r="AT155" s="3"/>
       <c r="AU155" s="3"/>
-    </row>
-    <row r="156" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV155" s="3"/>
+      <c r="AW155" s="3"/>
+      <c r="AX155" s="3"/>
+      <c r="AY155" s="3"/>
+    </row>
+    <row r="156" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -9163,8 +9832,12 @@
       <c r="AS156" s="3"/>
       <c r="AT156" s="3"/>
       <c r="AU156" s="3"/>
-    </row>
-    <row r="157" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV156" s="3"/>
+      <c r="AW156" s="3"/>
+      <c r="AX156" s="3"/>
+      <c r="AY156" s="3"/>
+    </row>
+    <row r="157" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -9210,8 +9883,12 @@
       <c r="AS157" s="3"/>
       <c r="AT157" s="3"/>
       <c r="AU157" s="3"/>
-    </row>
-    <row r="158" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV157" s="3"/>
+      <c r="AW157" s="3"/>
+      <c r="AX157" s="3"/>
+      <c r="AY157" s="3"/>
+    </row>
+    <row r="158" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -9257,8 +9934,12 @@
       <c r="AS158" s="3"/>
       <c r="AT158" s="3"/>
       <c r="AU158" s="3"/>
-    </row>
-    <row r="159" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV158" s="3"/>
+      <c r="AW158" s="3"/>
+      <c r="AX158" s="3"/>
+      <c r="AY158" s="3"/>
+    </row>
+    <row r="159" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -9304,8 +9985,12 @@
       <c r="AS159" s="3"/>
       <c r="AT159" s="3"/>
       <c r="AU159" s="3"/>
-    </row>
-    <row r="160" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV159" s="3"/>
+      <c r="AW159" s="3"/>
+      <c r="AX159" s="3"/>
+      <c r="AY159" s="3"/>
+    </row>
+    <row r="160" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -9351,8 +10036,12 @@
       <c r="AS160" s="3"/>
       <c r="AT160" s="3"/>
       <c r="AU160" s="3"/>
-    </row>
-    <row r="161" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV160" s="3"/>
+      <c r="AW160" s="3"/>
+      <c r="AX160" s="3"/>
+      <c r="AY160" s="3"/>
+    </row>
+    <row r="161" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -9398,8 +10087,12 @@
       <c r="AS161" s="3"/>
       <c r="AT161" s="3"/>
       <c r="AU161" s="3"/>
-    </row>
-    <row r="162" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV161" s="3"/>
+      <c r="AW161" s="3"/>
+      <c r="AX161" s="3"/>
+      <c r="AY161" s="3"/>
+    </row>
+    <row r="162" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -9445,8 +10138,12 @@
       <c r="AS162" s="3"/>
       <c r="AT162" s="3"/>
       <c r="AU162" s="3"/>
-    </row>
-    <row r="163" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV162" s="3"/>
+      <c r="AW162" s="3"/>
+      <c r="AX162" s="3"/>
+      <c r="AY162" s="3"/>
+    </row>
+    <row r="163" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -9492,8 +10189,12 @@
       <c r="AS163" s="3"/>
       <c r="AT163" s="3"/>
       <c r="AU163" s="3"/>
-    </row>
-    <row r="164" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV163" s="3"/>
+      <c r="AW163" s="3"/>
+      <c r="AX163" s="3"/>
+      <c r="AY163" s="3"/>
+    </row>
+    <row r="164" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -9539,8 +10240,12 @@
       <c r="AS164" s="3"/>
       <c r="AT164" s="3"/>
       <c r="AU164" s="3"/>
-    </row>
-    <row r="165" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV164" s="3"/>
+      <c r="AW164" s="3"/>
+      <c r="AX164" s="3"/>
+      <c r="AY164" s="3"/>
+    </row>
+    <row r="165" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -9586,8 +10291,12 @@
       <c r="AS165" s="3"/>
       <c r="AT165" s="3"/>
       <c r="AU165" s="3"/>
-    </row>
-    <row r="166" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV165" s="3"/>
+      <c r="AW165" s="3"/>
+      <c r="AX165" s="3"/>
+      <c r="AY165" s="3"/>
+    </row>
+    <row r="166" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -9633,8 +10342,12 @@
       <c r="AS166" s="3"/>
       <c r="AT166" s="3"/>
       <c r="AU166" s="3"/>
-    </row>
-    <row r="167" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV166" s="3"/>
+      <c r="AW166" s="3"/>
+      <c r="AX166" s="3"/>
+      <c r="AY166" s="3"/>
+    </row>
+    <row r="167" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -9680,8 +10393,12 @@
       <c r="AS167" s="3"/>
       <c r="AT167" s="3"/>
       <c r="AU167" s="3"/>
-    </row>
-    <row r="168" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV167" s="3"/>
+      <c r="AW167" s="3"/>
+      <c r="AX167" s="3"/>
+      <c r="AY167" s="3"/>
+    </row>
+    <row r="168" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -9727,8 +10444,12 @@
       <c r="AS168" s="3"/>
       <c r="AT168" s="3"/>
       <c r="AU168" s="3"/>
-    </row>
-    <row r="169" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV168" s="3"/>
+      <c r="AW168" s="3"/>
+      <c r="AX168" s="3"/>
+      <c r="AY168" s="3"/>
+    </row>
+    <row r="169" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -9774,8 +10495,12 @@
       <c r="AS169" s="3"/>
       <c r="AT169" s="3"/>
       <c r="AU169" s="3"/>
-    </row>
-    <row r="170" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV169" s="3"/>
+      <c r="AW169" s="3"/>
+      <c r="AX169" s="3"/>
+      <c r="AY169" s="3"/>
+    </row>
+    <row r="170" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -9821,8 +10546,12 @@
       <c r="AS170" s="3"/>
       <c r="AT170" s="3"/>
       <c r="AU170" s="3"/>
-    </row>
-    <row r="171" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV170" s="3"/>
+      <c r="AW170" s="3"/>
+      <c r="AX170" s="3"/>
+      <c r="AY170" s="3"/>
+    </row>
+    <row r="171" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -9868,8 +10597,12 @@
       <c r="AS171" s="3"/>
       <c r="AT171" s="3"/>
       <c r="AU171" s="3"/>
-    </row>
-    <row r="172" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV171" s="3"/>
+      <c r="AW171" s="3"/>
+      <c r="AX171" s="3"/>
+      <c r="AY171" s="3"/>
+    </row>
+    <row r="172" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -9915,8 +10648,12 @@
       <c r="AS172" s="3"/>
       <c r="AT172" s="3"/>
       <c r="AU172" s="3"/>
-    </row>
-    <row r="173" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV172" s="3"/>
+      <c r="AW172" s="3"/>
+      <c r="AX172" s="3"/>
+      <c r="AY172" s="3"/>
+    </row>
+    <row r="173" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -9962,8 +10699,12 @@
       <c r="AS173" s="3"/>
       <c r="AT173" s="3"/>
       <c r="AU173" s="3"/>
-    </row>
-    <row r="174" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV173" s="3"/>
+      <c r="AW173" s="3"/>
+      <c r="AX173" s="3"/>
+      <c r="AY173" s="3"/>
+    </row>
+    <row r="174" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -10009,8 +10750,12 @@
       <c r="AS174" s="3"/>
       <c r="AT174" s="3"/>
       <c r="AU174" s="3"/>
-    </row>
-    <row r="175" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV174" s="3"/>
+      <c r="AW174" s="3"/>
+      <c r="AX174" s="3"/>
+      <c r="AY174" s="3"/>
+    </row>
+    <row r="175" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -10056,8 +10801,12 @@
       <c r="AS175" s="3"/>
       <c r="AT175" s="3"/>
       <c r="AU175" s="3"/>
-    </row>
-    <row r="176" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV175" s="3"/>
+      <c r="AW175" s="3"/>
+      <c r="AX175" s="3"/>
+      <c r="AY175" s="3"/>
+    </row>
+    <row r="176" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -10103,8 +10852,12 @@
       <c r="AS176" s="3"/>
       <c r="AT176" s="3"/>
       <c r="AU176" s="3"/>
-    </row>
-    <row r="177" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV176" s="3"/>
+      <c r="AW176" s="3"/>
+      <c r="AX176" s="3"/>
+      <c r="AY176" s="3"/>
+    </row>
+    <row r="177" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -10150,8 +10903,12 @@
       <c r="AS177" s="3"/>
       <c r="AT177" s="3"/>
       <c r="AU177" s="3"/>
-    </row>
-    <row r="178" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV177" s="3"/>
+      <c r="AW177" s="3"/>
+      <c r="AX177" s="3"/>
+      <c r="AY177" s="3"/>
+    </row>
+    <row r="178" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -10197,8 +10954,12 @@
       <c r="AS178" s="3"/>
       <c r="AT178" s="3"/>
       <c r="AU178" s="3"/>
-    </row>
-    <row r="179" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV178" s="3"/>
+      <c r="AW178" s="3"/>
+      <c r="AX178" s="3"/>
+      <c r="AY178" s="3"/>
+    </row>
+    <row r="179" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -10244,8 +11005,12 @@
       <c r="AS179" s="3"/>
       <c r="AT179" s="3"/>
       <c r="AU179" s="3"/>
-    </row>
-    <row r="180" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV179" s="3"/>
+      <c r="AW179" s="3"/>
+      <c r="AX179" s="3"/>
+      <c r="AY179" s="3"/>
+    </row>
+    <row r="180" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -10291,8 +11056,12 @@
       <c r="AS180" s="3"/>
       <c r="AT180" s="3"/>
       <c r="AU180" s="3"/>
-    </row>
-    <row r="181" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV180" s="3"/>
+      <c r="AW180" s="3"/>
+      <c r="AX180" s="3"/>
+      <c r="AY180" s="3"/>
+    </row>
+    <row r="181" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -10338,8 +11107,12 @@
       <c r="AS181" s="3"/>
       <c r="AT181" s="3"/>
       <c r="AU181" s="3"/>
-    </row>
-    <row r="182" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV181" s="3"/>
+      <c r="AW181" s="3"/>
+      <c r="AX181" s="3"/>
+      <c r="AY181" s="3"/>
+    </row>
+    <row r="182" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -10385,8 +11158,12 @@
       <c r="AS182" s="3"/>
       <c r="AT182" s="3"/>
       <c r="AU182" s="3"/>
-    </row>
-    <row r="183" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV182" s="3"/>
+      <c r="AW182" s="3"/>
+      <c r="AX182" s="3"/>
+      <c r="AY182" s="3"/>
+    </row>
+    <row r="183" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -10432,8 +11209,12 @@
       <c r="AS183" s="3"/>
       <c r="AT183" s="3"/>
       <c r="AU183" s="3"/>
-    </row>
-    <row r="184" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV183" s="3"/>
+      <c r="AW183" s="3"/>
+      <c r="AX183" s="3"/>
+      <c r="AY183" s="3"/>
+    </row>
+    <row r="184" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -10479,8 +11260,12 @@
       <c r="AS184" s="3"/>
       <c r="AT184" s="3"/>
       <c r="AU184" s="3"/>
-    </row>
-    <row r="185" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV184" s="3"/>
+      <c r="AW184" s="3"/>
+      <c r="AX184" s="3"/>
+      <c r="AY184" s="3"/>
+    </row>
+    <row r="185" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -10526,8 +11311,12 @@
       <c r="AS185" s="3"/>
       <c r="AT185" s="3"/>
       <c r="AU185" s="3"/>
-    </row>
-    <row r="186" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV185" s="3"/>
+      <c r="AW185" s="3"/>
+      <c r="AX185" s="3"/>
+      <c r="AY185" s="3"/>
+    </row>
+    <row r="186" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -10573,8 +11362,12 @@
       <c r="AS186" s="3"/>
       <c r="AT186" s="3"/>
       <c r="AU186" s="3"/>
-    </row>
-    <row r="187" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV186" s="3"/>
+      <c r="AW186" s="3"/>
+      <c r="AX186" s="3"/>
+      <c r="AY186" s="3"/>
+    </row>
+    <row r="187" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -10620,8 +11413,12 @@
       <c r="AS187" s="3"/>
       <c r="AT187" s="3"/>
       <c r="AU187" s="3"/>
-    </row>
-    <row r="188" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV187" s="3"/>
+      <c r="AW187" s="3"/>
+      <c r="AX187" s="3"/>
+      <c r="AY187" s="3"/>
+    </row>
+    <row r="188" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -10667,8 +11464,12 @@
       <c r="AS188" s="3"/>
       <c r="AT188" s="3"/>
       <c r="AU188" s="3"/>
-    </row>
-    <row r="189" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV188" s="3"/>
+      <c r="AW188" s="3"/>
+      <c r="AX188" s="3"/>
+      <c r="AY188" s="3"/>
+    </row>
+    <row r="189" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -10714,8 +11515,12 @@
       <c r="AS189" s="3"/>
       <c r="AT189" s="3"/>
       <c r="AU189" s="3"/>
-    </row>
-    <row r="190" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV189" s="3"/>
+      <c r="AW189" s="3"/>
+      <c r="AX189" s="3"/>
+      <c r="AY189" s="3"/>
+    </row>
+    <row r="190" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -10761,8 +11566,12 @@
       <c r="AS190" s="3"/>
       <c r="AT190" s="3"/>
       <c r="AU190" s="3"/>
-    </row>
-    <row r="191" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV190" s="3"/>
+      <c r="AW190" s="3"/>
+      <c r="AX190" s="3"/>
+      <c r="AY190" s="3"/>
+    </row>
+    <row r="191" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -10808,8 +11617,12 @@
       <c r="AS191" s="3"/>
       <c r="AT191" s="3"/>
       <c r="AU191" s="3"/>
-    </row>
-    <row r="192" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV191" s="3"/>
+      <c r="AW191" s="3"/>
+      <c r="AX191" s="3"/>
+      <c r="AY191" s="3"/>
+    </row>
+    <row r="192" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -10855,8 +11668,12 @@
       <c r="AS192" s="3"/>
       <c r="AT192" s="3"/>
       <c r="AU192" s="3"/>
-    </row>
-    <row r="193" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV192" s="3"/>
+      <c r="AW192" s="3"/>
+      <c r="AX192" s="3"/>
+      <c r="AY192" s="3"/>
+    </row>
+    <row r="193" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -10902,8 +11719,12 @@
       <c r="AS193" s="3"/>
       <c r="AT193" s="3"/>
       <c r="AU193" s="3"/>
-    </row>
-    <row r="194" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV193" s="3"/>
+      <c r="AW193" s="3"/>
+      <c r="AX193" s="3"/>
+      <c r="AY193" s="3"/>
+    </row>
+    <row r="194" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -10949,8 +11770,12 @@
       <c r="AS194" s="3"/>
       <c r="AT194" s="3"/>
       <c r="AU194" s="3"/>
-    </row>
-    <row r="195" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV194" s="3"/>
+      <c r="AW194" s="3"/>
+      <c r="AX194" s="3"/>
+      <c r="AY194" s="3"/>
+    </row>
+    <row r="195" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -10996,8 +11821,12 @@
       <c r="AS195" s="3"/>
       <c r="AT195" s="3"/>
       <c r="AU195" s="3"/>
-    </row>
-    <row r="196" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV195" s="3"/>
+      <c r="AW195" s="3"/>
+      <c r="AX195" s="3"/>
+      <c r="AY195" s="3"/>
+    </row>
+    <row r="196" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -11043,8 +11872,12 @@
       <c r="AS196" s="3"/>
       <c r="AT196" s="3"/>
       <c r="AU196" s="3"/>
-    </row>
-    <row r="197" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV196" s="3"/>
+      <c r="AW196" s="3"/>
+      <c r="AX196" s="3"/>
+      <c r="AY196" s="3"/>
+    </row>
+    <row r="197" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -11090,8 +11923,12 @@
       <c r="AS197" s="3"/>
       <c r="AT197" s="3"/>
       <c r="AU197" s="3"/>
-    </row>
-    <row r="198" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV197" s="3"/>
+      <c r="AW197" s="3"/>
+      <c r="AX197" s="3"/>
+      <c r="AY197" s="3"/>
+    </row>
+    <row r="198" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -11137,8 +11974,12 @@
       <c r="AS198" s="3"/>
       <c r="AT198" s="3"/>
       <c r="AU198" s="3"/>
-    </row>
-    <row r="199" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV198" s="3"/>
+      <c r="AW198" s="3"/>
+      <c r="AX198" s="3"/>
+      <c r="AY198" s="3"/>
+    </row>
+    <row r="199" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -11184,8 +12025,12 @@
       <c r="AS199" s="3"/>
       <c r="AT199" s="3"/>
       <c r="AU199" s="3"/>
-    </row>
-    <row r="200" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV199" s="3"/>
+      <c r="AW199" s="3"/>
+      <c r="AX199" s="3"/>
+      <c r="AY199" s="3"/>
+    </row>
+    <row r="200" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -11231,8 +12076,12 @@
       <c r="AS200" s="3"/>
       <c r="AT200" s="3"/>
       <c r="AU200" s="3"/>
-    </row>
-    <row r="201" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV200" s="3"/>
+      <c r="AW200" s="3"/>
+      <c r="AX200" s="3"/>
+      <c r="AY200" s="3"/>
+    </row>
+    <row r="201" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -11278,8 +12127,12 @@
       <c r="AS201" s="3"/>
       <c r="AT201" s="3"/>
       <c r="AU201" s="3"/>
-    </row>
-    <row r="202" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV201" s="3"/>
+      <c r="AW201" s="3"/>
+      <c r="AX201" s="3"/>
+      <c r="AY201" s="3"/>
+    </row>
+    <row r="202" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -11325,8 +12178,12 @@
       <c r="AS202" s="3"/>
       <c r="AT202" s="3"/>
       <c r="AU202" s="3"/>
-    </row>
-    <row r="203" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV202" s="3"/>
+      <c r="AW202" s="3"/>
+      <c r="AX202" s="3"/>
+      <c r="AY202" s="3"/>
+    </row>
+    <row r="203" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -11372,8 +12229,12 @@
       <c r="AS203" s="3"/>
       <c r="AT203" s="3"/>
       <c r="AU203" s="3"/>
-    </row>
-    <row r="204" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV203" s="3"/>
+      <c r="AW203" s="3"/>
+      <c r="AX203" s="3"/>
+      <c r="AY203" s="3"/>
+    </row>
+    <row r="204" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -11419,8 +12280,12 @@
       <c r="AS204" s="3"/>
       <c r="AT204" s="3"/>
       <c r="AU204" s="3"/>
-    </row>
-    <row r="205" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV204" s="3"/>
+      <c r="AW204" s="3"/>
+      <c r="AX204" s="3"/>
+      <c r="AY204" s="3"/>
+    </row>
+    <row r="205" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -11466,8 +12331,12 @@
       <c r="AS205" s="3"/>
       <c r="AT205" s="3"/>
       <c r="AU205" s="3"/>
-    </row>
-    <row r="206" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV205" s="3"/>
+      <c r="AW205" s="3"/>
+      <c r="AX205" s="3"/>
+      <c r="AY205" s="3"/>
+    </row>
+    <row r="206" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -11513,8 +12382,12 @@
       <c r="AS206" s="3"/>
       <c r="AT206" s="3"/>
       <c r="AU206" s="3"/>
-    </row>
-    <row r="207" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV206" s="3"/>
+      <c r="AW206" s="3"/>
+      <c r="AX206" s="3"/>
+      <c r="AY206" s="3"/>
+    </row>
+    <row r="207" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -11560,8 +12433,12 @@
       <c r="AS207" s="3"/>
       <c r="AT207" s="3"/>
       <c r="AU207" s="3"/>
-    </row>
-    <row r="208" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV207" s="3"/>
+      <c r="AW207" s="3"/>
+      <c r="AX207" s="3"/>
+      <c r="AY207" s="3"/>
+    </row>
+    <row r="208" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -11607,8 +12484,12 @@
       <c r="AS208" s="3"/>
       <c r="AT208" s="3"/>
       <c r="AU208" s="3"/>
-    </row>
-    <row r="209" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV208" s="3"/>
+      <c r="AW208" s="3"/>
+      <c r="AX208" s="3"/>
+      <c r="AY208" s="3"/>
+    </row>
+    <row r="209" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -11654,8 +12535,12 @@
       <c r="AS209" s="3"/>
       <c r="AT209" s="3"/>
       <c r="AU209" s="3"/>
-    </row>
-    <row r="210" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV209" s="3"/>
+      <c r="AW209" s="3"/>
+      <c r="AX209" s="3"/>
+      <c r="AY209" s="3"/>
+    </row>
+    <row r="210" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -11701,8 +12586,12 @@
       <c r="AS210" s="3"/>
       <c r="AT210" s="3"/>
       <c r="AU210" s="3"/>
-    </row>
-    <row r="211" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV210" s="3"/>
+      <c r="AW210" s="3"/>
+      <c r="AX210" s="3"/>
+      <c r="AY210" s="3"/>
+    </row>
+    <row r="211" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -11748,8 +12637,12 @@
       <c r="AS211" s="3"/>
       <c r="AT211" s="3"/>
       <c r="AU211" s="3"/>
-    </row>
-    <row r="212" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV211" s="3"/>
+      <c r="AW211" s="3"/>
+      <c r="AX211" s="3"/>
+      <c r="AY211" s="3"/>
+    </row>
+    <row r="212" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -11795,8 +12688,12 @@
       <c r="AS212" s="3"/>
       <c r="AT212" s="3"/>
       <c r="AU212" s="3"/>
-    </row>
-    <row r="213" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV212" s="3"/>
+      <c r="AW212" s="3"/>
+      <c r="AX212" s="3"/>
+      <c r="AY212" s="3"/>
+    </row>
+    <row r="213" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -11842,8 +12739,12 @@
       <c r="AS213" s="3"/>
       <c r="AT213" s="3"/>
       <c r="AU213" s="3"/>
-    </row>
-    <row r="214" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV213" s="3"/>
+      <c r="AW213" s="3"/>
+      <c r="AX213" s="3"/>
+      <c r="AY213" s="3"/>
+    </row>
+    <row r="214" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -11889,8 +12790,12 @@
       <c r="AS214" s="3"/>
       <c r="AT214" s="3"/>
       <c r="AU214" s="3"/>
-    </row>
-    <row r="215" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV214" s="3"/>
+      <c r="AW214" s="3"/>
+      <c r="AX214" s="3"/>
+      <c r="AY214" s="3"/>
+    </row>
+    <row r="215" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -11936,8 +12841,12 @@
       <c r="AS215" s="3"/>
       <c r="AT215" s="3"/>
       <c r="AU215" s="3"/>
-    </row>
-    <row r="216" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV215" s="3"/>
+      <c r="AW215" s="3"/>
+      <c r="AX215" s="3"/>
+      <c r="AY215" s="3"/>
+    </row>
+    <row r="216" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -11983,8 +12892,12 @@
       <c r="AS216" s="3"/>
       <c r="AT216" s="3"/>
       <c r="AU216" s="3"/>
-    </row>
-    <row r="217" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV216" s="3"/>
+      <c r="AW216" s="3"/>
+      <c r="AX216" s="3"/>
+      <c r="AY216" s="3"/>
+    </row>
+    <row r="217" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -12030,8 +12943,12 @@
       <c r="AS217" s="3"/>
       <c r="AT217" s="3"/>
       <c r="AU217" s="3"/>
-    </row>
-    <row r="218" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV217" s="3"/>
+      <c r="AW217" s="3"/>
+      <c r="AX217" s="3"/>
+      <c r="AY217" s="3"/>
+    </row>
+    <row r="218" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -12077,8 +12994,12 @@
       <c r="AS218" s="3"/>
       <c r="AT218" s="3"/>
       <c r="AU218" s="3"/>
-    </row>
-    <row r="219" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV218" s="3"/>
+      <c r="AW218" s="3"/>
+      <c r="AX218" s="3"/>
+      <c r="AY218" s="3"/>
+    </row>
+    <row r="219" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -12124,8 +13045,12 @@
       <c r="AS219" s="3"/>
       <c r="AT219" s="3"/>
       <c r="AU219" s="3"/>
-    </row>
-    <row r="220" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV219" s="3"/>
+      <c r="AW219" s="3"/>
+      <c r="AX219" s="3"/>
+      <c r="AY219" s="3"/>
+    </row>
+    <row r="220" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -12171,8 +13096,12 @@
       <c r="AS220" s="3"/>
       <c r="AT220" s="3"/>
       <c r="AU220" s="3"/>
-    </row>
-    <row r="221" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV220" s="3"/>
+      <c r="AW220" s="3"/>
+      <c r="AX220" s="3"/>
+      <c r="AY220" s="3"/>
+    </row>
+    <row r="221" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -12218,8 +13147,12 @@
       <c r="AS221" s="3"/>
       <c r="AT221" s="3"/>
       <c r="AU221" s="3"/>
-    </row>
-    <row r="222" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV221" s="3"/>
+      <c r="AW221" s="3"/>
+      <c r="AX221" s="3"/>
+      <c r="AY221" s="3"/>
+    </row>
+    <row r="222" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -12265,8 +13198,12 @@
       <c r="AS222" s="3"/>
       <c r="AT222" s="3"/>
       <c r="AU222" s="3"/>
-    </row>
-    <row r="223" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV222" s="3"/>
+      <c r="AW222" s="3"/>
+      <c r="AX222" s="3"/>
+      <c r="AY222" s="3"/>
+    </row>
+    <row r="223" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -12312,8 +13249,12 @@
       <c r="AS223" s="3"/>
       <c r="AT223" s="3"/>
       <c r="AU223" s="3"/>
-    </row>
-    <row r="224" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV223" s="3"/>
+      <c r="AW223" s="3"/>
+      <c r="AX223" s="3"/>
+      <c r="AY223" s="3"/>
+    </row>
+    <row r="224" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -12359,8 +13300,12 @@
       <c r="AS224" s="3"/>
       <c r="AT224" s="3"/>
       <c r="AU224" s="3"/>
-    </row>
-    <row r="225" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV224" s="3"/>
+      <c r="AW224" s="3"/>
+      <c r="AX224" s="3"/>
+      <c r="AY224" s="3"/>
+    </row>
+    <row r="225" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -12406,8 +13351,12 @@
       <c r="AS225" s="3"/>
       <c r="AT225" s="3"/>
       <c r="AU225" s="3"/>
-    </row>
-    <row r="226" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV225" s="3"/>
+      <c r="AW225" s="3"/>
+      <c r="AX225" s="3"/>
+      <c r="AY225" s="3"/>
+    </row>
+    <row r="226" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -12453,8 +13402,12 @@
       <c r="AS226" s="3"/>
       <c r="AT226" s="3"/>
       <c r="AU226" s="3"/>
-    </row>
-    <row r="227" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV226" s="3"/>
+      <c r="AW226" s="3"/>
+      <c r="AX226" s="3"/>
+      <c r="AY226" s="3"/>
+    </row>
+    <row r="227" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -12500,8 +13453,12 @@
       <c r="AS227" s="3"/>
       <c r="AT227" s="3"/>
       <c r="AU227" s="3"/>
-    </row>
-    <row r="228" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV227" s="3"/>
+      <c r="AW227" s="3"/>
+      <c r="AX227" s="3"/>
+      <c r="AY227" s="3"/>
+    </row>
+    <row r="228" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -12547,8 +13504,12 @@
       <c r="AS228" s="3"/>
       <c r="AT228" s="3"/>
       <c r="AU228" s="3"/>
-    </row>
-    <row r="229" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV228" s="3"/>
+      <c r="AW228" s="3"/>
+      <c r="AX228" s="3"/>
+      <c r="AY228" s="3"/>
+    </row>
+    <row r="229" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -12594,8 +13555,12 @@
       <c r="AS229" s="3"/>
       <c r="AT229" s="3"/>
       <c r="AU229" s="3"/>
-    </row>
-    <row r="230" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV229" s="3"/>
+      <c r="AW229" s="3"/>
+      <c r="AX229" s="3"/>
+      <c r="AY229" s="3"/>
+    </row>
+    <row r="230" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -12641,8 +13606,12 @@
       <c r="AS230" s="3"/>
       <c r="AT230" s="3"/>
       <c r="AU230" s="3"/>
-    </row>
-    <row r="231" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV230" s="3"/>
+      <c r="AW230" s="3"/>
+      <c r="AX230" s="3"/>
+      <c r="AY230" s="3"/>
+    </row>
+    <row r="231" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -12688,8 +13657,12 @@
       <c r="AS231" s="3"/>
       <c r="AT231" s="3"/>
       <c r="AU231" s="3"/>
-    </row>
-    <row r="232" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV231" s="3"/>
+      <c r="AW231" s="3"/>
+      <c r="AX231" s="3"/>
+      <c r="AY231" s="3"/>
+    </row>
+    <row r="232" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -12735,8 +13708,12 @@
       <c r="AS232" s="3"/>
       <c r="AT232" s="3"/>
       <c r="AU232" s="3"/>
-    </row>
-    <row r="233" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV232" s="3"/>
+      <c r="AW232" s="3"/>
+      <c r="AX232" s="3"/>
+      <c r="AY232" s="3"/>
+    </row>
+    <row r="233" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -12782,8 +13759,12 @@
       <c r="AS233" s="3"/>
       <c r="AT233" s="3"/>
       <c r="AU233" s="3"/>
-    </row>
-    <row r="234" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV233" s="3"/>
+      <c r="AW233" s="3"/>
+      <c r="AX233" s="3"/>
+      <c r="AY233" s="3"/>
+    </row>
+    <row r="234" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -12829,8 +13810,12 @@
       <c r="AS234" s="3"/>
       <c r="AT234" s="3"/>
       <c r="AU234" s="3"/>
-    </row>
-    <row r="235" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV234" s="3"/>
+      <c r="AW234" s="3"/>
+      <c r="AX234" s="3"/>
+      <c r="AY234" s="3"/>
+    </row>
+    <row r="235" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -12876,8 +13861,12 @@
       <c r="AS235" s="3"/>
       <c r="AT235" s="3"/>
       <c r="AU235" s="3"/>
-    </row>
-    <row r="236" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV235" s="3"/>
+      <c r="AW235" s="3"/>
+      <c r="AX235" s="3"/>
+      <c r="AY235" s="3"/>
+    </row>
+    <row r="236" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -12923,8 +13912,12 @@
       <c r="AS236" s="3"/>
       <c r="AT236" s="3"/>
       <c r="AU236" s="3"/>
-    </row>
-    <row r="237" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV236" s="3"/>
+      <c r="AW236" s="3"/>
+      <c r="AX236" s="3"/>
+      <c r="AY236" s="3"/>
+    </row>
+    <row r="237" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -12970,8 +13963,12 @@
       <c r="AS237" s="3"/>
       <c r="AT237" s="3"/>
       <c r="AU237" s="3"/>
-    </row>
-    <row r="238" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV237" s="3"/>
+      <c r="AW237" s="3"/>
+      <c r="AX237" s="3"/>
+      <c r="AY237" s="3"/>
+    </row>
+    <row r="238" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -13017,8 +14014,12 @@
       <c r="AS238" s="3"/>
       <c r="AT238" s="3"/>
       <c r="AU238" s="3"/>
-    </row>
-    <row r="239" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV238" s="3"/>
+      <c r="AW238" s="3"/>
+      <c r="AX238" s="3"/>
+      <c r="AY238" s="3"/>
+    </row>
+    <row r="239" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -13064,8 +14065,12 @@
       <c r="AS239" s="3"/>
       <c r="AT239" s="3"/>
       <c r="AU239" s="3"/>
-    </row>
-    <row r="240" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV239" s="3"/>
+      <c r="AW239" s="3"/>
+      <c r="AX239" s="3"/>
+      <c r="AY239" s="3"/>
+    </row>
+    <row r="240" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -13111,8 +14116,12 @@
       <c r="AS240" s="3"/>
       <c r="AT240" s="3"/>
       <c r="AU240" s="3"/>
-    </row>
-    <row r="241" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV240" s="3"/>
+      <c r="AW240" s="3"/>
+      <c r="AX240" s="3"/>
+      <c r="AY240" s="3"/>
+    </row>
+    <row r="241" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -13158,8 +14167,12 @@
       <c r="AS241" s="3"/>
       <c r="AT241" s="3"/>
       <c r="AU241" s="3"/>
-    </row>
-    <row r="242" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV241" s="3"/>
+      <c r="AW241" s="3"/>
+      <c r="AX241" s="3"/>
+      <c r="AY241" s="3"/>
+    </row>
+    <row r="242" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -13205,8 +14218,12 @@
       <c r="AS242" s="3"/>
       <c r="AT242" s="3"/>
       <c r="AU242" s="3"/>
-    </row>
-    <row r="243" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV242" s="3"/>
+      <c r="AW242" s="3"/>
+      <c r="AX242" s="3"/>
+      <c r="AY242" s="3"/>
+    </row>
+    <row r="243" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -13252,8 +14269,12 @@
       <c r="AS243" s="3"/>
       <c r="AT243" s="3"/>
       <c r="AU243" s="3"/>
-    </row>
-    <row r="244" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV243" s="3"/>
+      <c r="AW243" s="3"/>
+      <c r="AX243" s="3"/>
+      <c r="AY243" s="3"/>
+    </row>
+    <row r="244" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -13299,8 +14320,12 @@
       <c r="AS244" s="3"/>
       <c r="AT244" s="3"/>
       <c r="AU244" s="3"/>
-    </row>
-    <row r="245" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV244" s="3"/>
+      <c r="AW244" s="3"/>
+      <c r="AX244" s="3"/>
+      <c r="AY244" s="3"/>
+    </row>
+    <row r="245" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -13346,8 +14371,12 @@
       <c r="AS245" s="3"/>
       <c r="AT245" s="3"/>
       <c r="AU245" s="3"/>
-    </row>
-    <row r="246" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV245" s="3"/>
+      <c r="AW245" s="3"/>
+      <c r="AX245" s="3"/>
+      <c r="AY245" s="3"/>
+    </row>
+    <row r="246" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -13393,8 +14422,12 @@
       <c r="AS246" s="3"/>
       <c r="AT246" s="3"/>
       <c r="AU246" s="3"/>
-    </row>
-    <row r="247" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV246" s="3"/>
+      <c r="AW246" s="3"/>
+      <c r="AX246" s="3"/>
+      <c r="AY246" s="3"/>
+    </row>
+    <row r="247" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -13440,8 +14473,12 @@
       <c r="AS247" s="3"/>
       <c r="AT247" s="3"/>
       <c r="AU247" s="3"/>
-    </row>
-    <row r="248" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV247" s="3"/>
+      <c r="AW247" s="3"/>
+      <c r="AX247" s="3"/>
+      <c r="AY247" s="3"/>
+    </row>
+    <row r="248" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -13487,8 +14524,12 @@
       <c r="AS248" s="3"/>
       <c r="AT248" s="3"/>
       <c r="AU248" s="3"/>
-    </row>
-    <row r="249" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV248" s="3"/>
+      <c r="AW248" s="3"/>
+      <c r="AX248" s="3"/>
+      <c r="AY248" s="3"/>
+    </row>
+    <row r="249" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -13534,8 +14575,12 @@
       <c r="AS249" s="3"/>
       <c r="AT249" s="3"/>
       <c r="AU249" s="3"/>
-    </row>
-    <row r="250" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV249" s="3"/>
+      <c r="AW249" s="3"/>
+      <c r="AX249" s="3"/>
+      <c r="AY249" s="3"/>
+    </row>
+    <row r="250" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -13581,8 +14626,12 @@
       <c r="AS250" s="3"/>
       <c r="AT250" s="3"/>
       <c r="AU250" s="3"/>
-    </row>
-    <row r="251" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV250" s="3"/>
+      <c r="AW250" s="3"/>
+      <c r="AX250" s="3"/>
+      <c r="AY250" s="3"/>
+    </row>
+    <row r="251" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -13628,8 +14677,12 @@
       <c r="AS251" s="3"/>
       <c r="AT251" s="3"/>
       <c r="AU251" s="3"/>
-    </row>
-    <row r="252" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV251" s="3"/>
+      <c r="AW251" s="3"/>
+      <c r="AX251" s="3"/>
+      <c r="AY251" s="3"/>
+    </row>
+    <row r="252" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -13675,8 +14728,12 @@
       <c r="AS252" s="3"/>
       <c r="AT252" s="3"/>
       <c r="AU252" s="3"/>
-    </row>
-    <row r="253" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV252" s="3"/>
+      <c r="AW252" s="3"/>
+      <c r="AX252" s="3"/>
+      <c r="AY252" s="3"/>
+    </row>
+    <row r="253" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -13722,8 +14779,12 @@
       <c r="AS253" s="3"/>
       <c r="AT253" s="3"/>
       <c r="AU253" s="3"/>
-    </row>
-    <row r="254" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV253" s="3"/>
+      <c r="AW253" s="3"/>
+      <c r="AX253" s="3"/>
+      <c r="AY253" s="3"/>
+    </row>
+    <row r="254" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -13769,8 +14830,12 @@
       <c r="AS254" s="3"/>
       <c r="AT254" s="3"/>
       <c r="AU254" s="3"/>
-    </row>
-    <row r="255" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV254" s="3"/>
+      <c r="AW254" s="3"/>
+      <c r="AX254" s="3"/>
+      <c r="AY254" s="3"/>
+    </row>
+    <row r="255" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -13816,8 +14881,12 @@
       <c r="AS255" s="3"/>
       <c r="AT255" s="3"/>
       <c r="AU255" s="3"/>
-    </row>
-    <row r="256" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV255" s="3"/>
+      <c r="AW255" s="3"/>
+      <c r="AX255" s="3"/>
+      <c r="AY255" s="3"/>
+    </row>
+    <row r="256" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -13863,8 +14932,12 @@
       <c r="AS256" s="3"/>
       <c r="AT256" s="3"/>
       <c r="AU256" s="3"/>
-    </row>
-    <row r="257" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV256" s="3"/>
+      <c r="AW256" s="3"/>
+      <c r="AX256" s="3"/>
+      <c r="AY256" s="3"/>
+    </row>
+    <row r="257" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -13910,8 +14983,12 @@
       <c r="AS257" s="3"/>
       <c r="AT257" s="3"/>
       <c r="AU257" s="3"/>
-    </row>
-    <row r="258" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV257" s="3"/>
+      <c r="AW257" s="3"/>
+      <c r="AX257" s="3"/>
+      <c r="AY257" s="3"/>
+    </row>
+    <row r="258" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -13957,8 +15034,12 @@
       <c r="AS258" s="3"/>
       <c r="AT258" s="3"/>
       <c r="AU258" s="3"/>
-    </row>
-    <row r="259" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV258" s="3"/>
+      <c r="AW258" s="3"/>
+      <c r="AX258" s="3"/>
+      <c r="AY258" s="3"/>
+    </row>
+    <row r="259" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -14004,8 +15085,12 @@
       <c r="AS259" s="3"/>
       <c r="AT259" s="3"/>
       <c r="AU259" s="3"/>
-    </row>
-    <row r="260" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV259" s="3"/>
+      <c r="AW259" s="3"/>
+      <c r="AX259" s="3"/>
+      <c r="AY259" s="3"/>
+    </row>
+    <row r="260" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -14051,8 +15136,12 @@
       <c r="AS260" s="3"/>
       <c r="AT260" s="3"/>
       <c r="AU260" s="3"/>
-    </row>
-    <row r="261" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV260" s="3"/>
+      <c r="AW260" s="3"/>
+      <c r="AX260" s="3"/>
+      <c r="AY260" s="3"/>
+    </row>
+    <row r="261" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -14098,8 +15187,12 @@
       <c r="AS261" s="3"/>
       <c r="AT261" s="3"/>
       <c r="AU261" s="3"/>
-    </row>
-    <row r="262" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV261" s="3"/>
+      <c r="AW261" s="3"/>
+      <c r="AX261" s="3"/>
+      <c r="AY261" s="3"/>
+    </row>
+    <row r="262" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -14145,8 +15238,12 @@
       <c r="AS262" s="3"/>
       <c r="AT262" s="3"/>
       <c r="AU262" s="3"/>
-    </row>
-    <row r="263" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV262" s="3"/>
+      <c r="AW262" s="3"/>
+      <c r="AX262" s="3"/>
+      <c r="AY262" s="3"/>
+    </row>
+    <row r="263" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -14192,8 +15289,12 @@
       <c r="AS263" s="3"/>
       <c r="AT263" s="3"/>
       <c r="AU263" s="3"/>
-    </row>
-    <row r="264" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV263" s="3"/>
+      <c r="AW263" s="3"/>
+      <c r="AX263" s="3"/>
+      <c r="AY263" s="3"/>
+    </row>
+    <row r="264" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -14239,8 +15340,12 @@
       <c r="AS264" s="3"/>
       <c r="AT264" s="3"/>
       <c r="AU264" s="3"/>
-    </row>
-    <row r="265" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV264" s="3"/>
+      <c r="AW264" s="3"/>
+      <c r="AX264" s="3"/>
+      <c r="AY264" s="3"/>
+    </row>
+    <row r="265" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -14286,8 +15391,12 @@
       <c r="AS265" s="3"/>
       <c r="AT265" s="3"/>
       <c r="AU265" s="3"/>
-    </row>
-    <row r="266" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV265" s="3"/>
+      <c r="AW265" s="3"/>
+      <c r="AX265" s="3"/>
+      <c r="AY265" s="3"/>
+    </row>
+    <row r="266" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -14333,8 +15442,12 @@
       <c r="AS266" s="3"/>
       <c r="AT266" s="3"/>
       <c r="AU266" s="3"/>
-    </row>
-    <row r="267" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV266" s="3"/>
+      <c r="AW266" s="3"/>
+      <c r="AX266" s="3"/>
+      <c r="AY266" s="3"/>
+    </row>
+    <row r="267" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -14380,8 +15493,12 @@
       <c r="AS267" s="3"/>
       <c r="AT267" s="3"/>
       <c r="AU267" s="3"/>
-    </row>
-    <row r="268" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV267" s="3"/>
+      <c r="AW267" s="3"/>
+      <c r="AX267" s="3"/>
+      <c r="AY267" s="3"/>
+    </row>
+    <row r="268" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -14427,8 +15544,12 @@
       <c r="AS268" s="3"/>
       <c r="AT268" s="3"/>
       <c r="AU268" s="3"/>
-    </row>
-    <row r="269" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV268" s="3"/>
+      <c r="AW268" s="3"/>
+      <c r="AX268" s="3"/>
+      <c r="AY268" s="3"/>
+    </row>
+    <row r="269" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -14474,8 +15595,12 @@
       <c r="AS269" s="3"/>
       <c r="AT269" s="3"/>
       <c r="AU269" s="3"/>
-    </row>
-    <row r="270" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV269" s="3"/>
+      <c r="AW269" s="3"/>
+      <c r="AX269" s="3"/>
+      <c r="AY269" s="3"/>
+    </row>
+    <row r="270" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -14521,8 +15646,12 @@
       <c r="AS270" s="3"/>
       <c r="AT270" s="3"/>
       <c r="AU270" s="3"/>
-    </row>
-    <row r="271" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV270" s="3"/>
+      <c r="AW270" s="3"/>
+      <c r="AX270" s="3"/>
+      <c r="AY270" s="3"/>
+    </row>
+    <row r="271" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -14568,8 +15697,12 @@
       <c r="AS271" s="3"/>
       <c r="AT271" s="3"/>
       <c r="AU271" s="3"/>
-    </row>
-    <row r="272" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV271" s="3"/>
+      <c r="AW271" s="3"/>
+      <c r="AX271" s="3"/>
+      <c r="AY271" s="3"/>
+    </row>
+    <row r="272" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -14615,8 +15748,12 @@
       <c r="AS272" s="3"/>
       <c r="AT272" s="3"/>
       <c r="AU272" s="3"/>
-    </row>
-    <row r="273" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV272" s="3"/>
+      <c r="AW272" s="3"/>
+      <c r="AX272" s="3"/>
+      <c r="AY272" s="3"/>
+    </row>
+    <row r="273" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -14662,8 +15799,12 @@
       <c r="AS273" s="3"/>
       <c r="AT273" s="3"/>
       <c r="AU273" s="3"/>
-    </row>
-    <row r="274" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV273" s="3"/>
+      <c r="AW273" s="3"/>
+      <c r="AX273" s="3"/>
+      <c r="AY273" s="3"/>
+    </row>
+    <row r="274" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -14709,8 +15850,12 @@
       <c r="AS274" s="3"/>
       <c r="AT274" s="3"/>
       <c r="AU274" s="3"/>
-    </row>
-    <row r="275" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV274" s="3"/>
+      <c r="AW274" s="3"/>
+      <c r="AX274" s="3"/>
+      <c r="AY274" s="3"/>
+    </row>
+    <row r="275" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -14756,8 +15901,12 @@
       <c r="AS275" s="3"/>
       <c r="AT275" s="3"/>
       <c r="AU275" s="3"/>
-    </row>
-    <row r="276" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV275" s="3"/>
+      <c r="AW275" s="3"/>
+      <c r="AX275" s="3"/>
+      <c r="AY275" s="3"/>
+    </row>
+    <row r="276" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -14803,8 +15952,12 @@
       <c r="AS276" s="3"/>
       <c r="AT276" s="3"/>
       <c r="AU276" s="3"/>
-    </row>
-    <row r="277" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV276" s="3"/>
+      <c r="AW276" s="3"/>
+      <c r="AX276" s="3"/>
+      <c r="AY276" s="3"/>
+    </row>
+    <row r="277" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -14850,8 +16003,12 @@
       <c r="AS277" s="3"/>
       <c r="AT277" s="3"/>
       <c r="AU277" s="3"/>
-    </row>
-    <row r="278" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV277" s="3"/>
+      <c r="AW277" s="3"/>
+      <c r="AX277" s="3"/>
+      <c r="AY277" s="3"/>
+    </row>
+    <row r="278" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -14897,8 +16054,12 @@
       <c r="AS278" s="3"/>
       <c r="AT278" s="3"/>
       <c r="AU278" s="3"/>
-    </row>
-    <row r="279" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV278" s="3"/>
+      <c r="AW278" s="3"/>
+      <c r="AX278" s="3"/>
+      <c r="AY278" s="3"/>
+    </row>
+    <row r="279" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -14944,8 +16105,12 @@
       <c r="AS279" s="3"/>
       <c r="AT279" s="3"/>
       <c r="AU279" s="3"/>
-    </row>
-    <row r="280" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV279" s="3"/>
+      <c r="AW279" s="3"/>
+      <c r="AX279" s="3"/>
+      <c r="AY279" s="3"/>
+    </row>
+    <row r="280" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -14991,8 +16156,12 @@
       <c r="AS280" s="3"/>
       <c r="AT280" s="3"/>
       <c r="AU280" s="3"/>
-    </row>
-    <row r="281" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV280" s="3"/>
+      <c r="AW280" s="3"/>
+      <c r="AX280" s="3"/>
+      <c r="AY280" s="3"/>
+    </row>
+    <row r="281" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -15038,8 +16207,12 @@
       <c r="AS281" s="3"/>
       <c r="AT281" s="3"/>
       <c r="AU281" s="3"/>
-    </row>
-    <row r="282" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV281" s="3"/>
+      <c r="AW281" s="3"/>
+      <c r="AX281" s="3"/>
+      <c r="AY281" s="3"/>
+    </row>
+    <row r="282" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -15085,8 +16258,12 @@
       <c r="AS282" s="3"/>
       <c r="AT282" s="3"/>
       <c r="AU282" s="3"/>
-    </row>
-    <row r="283" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV282" s="3"/>
+      <c r="AW282" s="3"/>
+      <c r="AX282" s="3"/>
+      <c r="AY282" s="3"/>
+    </row>
+    <row r="283" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -15132,8 +16309,12 @@
       <c r="AS283" s="3"/>
       <c r="AT283" s="3"/>
       <c r="AU283" s="3"/>
-    </row>
-    <row r="284" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV283" s="3"/>
+      <c r="AW283" s="3"/>
+      <c r="AX283" s="3"/>
+      <c r="AY283" s="3"/>
+    </row>
+    <row r="284" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -15179,8 +16360,12 @@
       <c r="AS284" s="3"/>
       <c r="AT284" s="3"/>
       <c r="AU284" s="3"/>
-    </row>
-    <row r="285" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV284" s="3"/>
+      <c r="AW284" s="3"/>
+      <c r="AX284" s="3"/>
+      <c r="AY284" s="3"/>
+    </row>
+    <row r="285" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -15226,8 +16411,12 @@
       <c r="AS285" s="3"/>
       <c r="AT285" s="3"/>
       <c r="AU285" s="3"/>
-    </row>
-    <row r="286" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV285" s="3"/>
+      <c r="AW285" s="3"/>
+      <c r="AX285" s="3"/>
+      <c r="AY285" s="3"/>
+    </row>
+    <row r="286" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -15273,8 +16462,12 @@
       <c r="AS286" s="3"/>
       <c r="AT286" s="3"/>
       <c r="AU286" s="3"/>
-    </row>
-    <row r="287" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV286" s="3"/>
+      <c r="AW286" s="3"/>
+      <c r="AX286" s="3"/>
+      <c r="AY286" s="3"/>
+    </row>
+    <row r="287" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -15320,8 +16513,12 @@
       <c r="AS287" s="3"/>
       <c r="AT287" s="3"/>
       <c r="AU287" s="3"/>
-    </row>
-    <row r="288" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV287" s="3"/>
+      <c r="AW287" s="3"/>
+      <c r="AX287" s="3"/>
+      <c r="AY287" s="3"/>
+    </row>
+    <row r="288" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -15367,8 +16564,12 @@
       <c r="AS288" s="3"/>
       <c r="AT288" s="3"/>
       <c r="AU288" s="3"/>
-    </row>
-    <row r="289" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV288" s="3"/>
+      <c r="AW288" s="3"/>
+      <c r="AX288" s="3"/>
+      <c r="AY288" s="3"/>
+    </row>
+    <row r="289" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -15414,8 +16615,12 @@
       <c r="AS289" s="3"/>
       <c r="AT289" s="3"/>
       <c r="AU289" s="3"/>
-    </row>
-    <row r="290" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV289" s="3"/>
+      <c r="AW289" s="3"/>
+      <c r="AX289" s="3"/>
+      <c r="AY289" s="3"/>
+    </row>
+    <row r="290" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -15461,8 +16666,12 @@
       <c r="AS290" s="3"/>
       <c r="AT290" s="3"/>
       <c r="AU290" s="3"/>
-    </row>
-    <row r="291" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV290" s="3"/>
+      <c r="AW290" s="3"/>
+      <c r="AX290" s="3"/>
+      <c r="AY290" s="3"/>
+    </row>
+    <row r="291" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -15508,8 +16717,12 @@
       <c r="AS291" s="3"/>
       <c r="AT291" s="3"/>
       <c r="AU291" s="3"/>
-    </row>
-    <row r="292" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV291" s="3"/>
+      <c r="AW291" s="3"/>
+      <c r="AX291" s="3"/>
+      <c r="AY291" s="3"/>
+    </row>
+    <row r="292" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -15555,8 +16768,12 @@
       <c r="AS292" s="3"/>
       <c r="AT292" s="3"/>
       <c r="AU292" s="3"/>
-    </row>
-    <row r="293" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV292" s="3"/>
+      <c r="AW292" s="3"/>
+      <c r="AX292" s="3"/>
+      <c r="AY292" s="3"/>
+    </row>
+    <row r="293" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -15602,8 +16819,12 @@
       <c r="AS293" s="3"/>
       <c r="AT293" s="3"/>
       <c r="AU293" s="3"/>
-    </row>
-    <row r="294" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV293" s="3"/>
+      <c r="AW293" s="3"/>
+      <c r="AX293" s="3"/>
+      <c r="AY293" s="3"/>
+    </row>
+    <row r="294" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -15649,8 +16870,12 @@
       <c r="AS294" s="3"/>
       <c r="AT294" s="3"/>
       <c r="AU294" s="3"/>
-    </row>
-    <row r="295" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV294" s="3"/>
+      <c r="AW294" s="3"/>
+      <c r="AX294" s="3"/>
+      <c r="AY294" s="3"/>
+    </row>
+    <row r="295" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -15696,8 +16921,12 @@
       <c r="AS295" s="3"/>
       <c r="AT295" s="3"/>
       <c r="AU295" s="3"/>
-    </row>
-    <row r="296" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV295" s="3"/>
+      <c r="AW295" s="3"/>
+      <c r="AX295" s="3"/>
+      <c r="AY295" s="3"/>
+    </row>
+    <row r="296" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -15743,8 +16972,12 @@
       <c r="AS296" s="3"/>
       <c r="AT296" s="3"/>
       <c r="AU296" s="3"/>
-    </row>
-    <row r="297" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV296" s="3"/>
+      <c r="AW296" s="3"/>
+      <c r="AX296" s="3"/>
+      <c r="AY296" s="3"/>
+    </row>
+    <row r="297" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -15790,8 +17023,12 @@
       <c r="AS297" s="3"/>
       <c r="AT297" s="3"/>
       <c r="AU297" s="3"/>
-    </row>
-    <row r="298" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV297" s="3"/>
+      <c r="AW297" s="3"/>
+      <c r="AX297" s="3"/>
+      <c r="AY297" s="3"/>
+    </row>
+    <row r="298" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -15837,8 +17074,12 @@
       <c r="AS298" s="3"/>
       <c r="AT298" s="3"/>
       <c r="AU298" s="3"/>
-    </row>
-    <row r="299" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV298" s="3"/>
+      <c r="AW298" s="3"/>
+      <c r="AX298" s="3"/>
+      <c r="AY298" s="3"/>
+    </row>
+    <row r="299" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -15884,8 +17125,12 @@
       <c r="AS299" s="3"/>
       <c r="AT299" s="3"/>
       <c r="AU299" s="3"/>
-    </row>
-    <row r="300" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV299" s="3"/>
+      <c r="AW299" s="3"/>
+      <c r="AX299" s="3"/>
+      <c r="AY299" s="3"/>
+    </row>
+    <row r="300" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -15931,8 +17176,12 @@
       <c r="AS300" s="3"/>
       <c r="AT300" s="3"/>
       <c r="AU300" s="3"/>
-    </row>
-    <row r="301" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV300" s="3"/>
+      <c r="AW300" s="3"/>
+      <c r="AX300" s="3"/>
+      <c r="AY300" s="3"/>
+    </row>
+    <row r="301" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -15978,8 +17227,12 @@
       <c r="AS301" s="3"/>
       <c r="AT301" s="3"/>
       <c r="AU301" s="3"/>
-    </row>
-    <row r="302" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV301" s="3"/>
+      <c r="AW301" s="3"/>
+      <c r="AX301" s="3"/>
+      <c r="AY301" s="3"/>
+    </row>
+    <row r="302" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -16025,8 +17278,12 @@
       <c r="AS302" s="3"/>
       <c r="AT302" s="3"/>
       <c r="AU302" s="3"/>
-    </row>
-    <row r="303" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV302" s="3"/>
+      <c r="AW302" s="3"/>
+      <c r="AX302" s="3"/>
+      <c r="AY302" s="3"/>
+    </row>
+    <row r="303" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -16072,8 +17329,12 @@
       <c r="AS303" s="3"/>
       <c r="AT303" s="3"/>
       <c r="AU303" s="3"/>
-    </row>
-    <row r="304" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV303" s="3"/>
+      <c r="AW303" s="3"/>
+      <c r="AX303" s="3"/>
+      <c r="AY303" s="3"/>
+    </row>
+    <row r="304" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -16119,8 +17380,12 @@
       <c r="AS304" s="3"/>
       <c r="AT304" s="3"/>
       <c r="AU304" s="3"/>
-    </row>
-    <row r="305" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV304" s="3"/>
+      <c r="AW304" s="3"/>
+      <c r="AX304" s="3"/>
+      <c r="AY304" s="3"/>
+    </row>
+    <row r="305" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -16166,8 +17431,12 @@
       <c r="AS305" s="3"/>
       <c r="AT305" s="3"/>
       <c r="AU305" s="3"/>
-    </row>
-    <row r="306" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV305" s="3"/>
+      <c r="AW305" s="3"/>
+      <c r="AX305" s="3"/>
+      <c r="AY305" s="3"/>
+    </row>
+    <row r="306" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -16213,8 +17482,12 @@
       <c r="AS306" s="3"/>
       <c r="AT306" s="3"/>
       <c r="AU306" s="3"/>
-    </row>
-    <row r="307" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV306" s="3"/>
+      <c r="AW306" s="3"/>
+      <c r="AX306" s="3"/>
+      <c r="AY306" s="3"/>
+    </row>
+    <row r="307" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -16260,8 +17533,12 @@
       <c r="AS307" s="3"/>
       <c r="AT307" s="3"/>
       <c r="AU307" s="3"/>
-    </row>
-    <row r="308" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV307" s="3"/>
+      <c r="AW307" s="3"/>
+      <c r="AX307" s="3"/>
+      <c r="AY307" s="3"/>
+    </row>
+    <row r="308" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -16307,8 +17584,12 @@
       <c r="AS308" s="3"/>
       <c r="AT308" s="3"/>
       <c r="AU308" s="3"/>
-    </row>
-    <row r="309" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV308" s="3"/>
+      <c r="AW308" s="3"/>
+      <c r="AX308" s="3"/>
+      <c r="AY308" s="3"/>
+    </row>
+    <row r="309" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -16354,8 +17635,12 @@
       <c r="AS309" s="3"/>
       <c r="AT309" s="3"/>
       <c r="AU309" s="3"/>
-    </row>
-    <row r="310" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV309" s="3"/>
+      <c r="AW309" s="3"/>
+      <c r="AX309" s="3"/>
+      <c r="AY309" s="3"/>
+    </row>
+    <row r="310" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -16401,8 +17686,12 @@
       <c r="AS310" s="3"/>
       <c r="AT310" s="3"/>
       <c r="AU310" s="3"/>
-    </row>
-    <row r="311" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV310" s="3"/>
+      <c r="AW310" s="3"/>
+      <c r="AX310" s="3"/>
+      <c r="AY310" s="3"/>
+    </row>
+    <row r="311" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -16448,8 +17737,12 @@
       <c r="AS311" s="3"/>
       <c r="AT311" s="3"/>
       <c r="AU311" s="3"/>
-    </row>
-    <row r="312" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV311" s="3"/>
+      <c r="AW311" s="3"/>
+      <c r="AX311" s="3"/>
+      <c r="AY311" s="3"/>
+    </row>
+    <row r="312" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -16495,8 +17788,12 @@
       <c r="AS312" s="3"/>
       <c r="AT312" s="3"/>
       <c r="AU312" s="3"/>
-    </row>
-    <row r="313" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV312" s="3"/>
+      <c r="AW312" s="3"/>
+      <c r="AX312" s="3"/>
+      <c r="AY312" s="3"/>
+    </row>
+    <row r="313" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -16542,8 +17839,12 @@
       <c r="AS313" s="3"/>
       <c r="AT313" s="3"/>
       <c r="AU313" s="3"/>
-    </row>
-    <row r="314" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV313" s="3"/>
+      <c r="AW313" s="3"/>
+      <c r="AX313" s="3"/>
+      <c r="AY313" s="3"/>
+    </row>
+    <row r="314" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -16589,8 +17890,12 @@
       <c r="AS314" s="3"/>
       <c r="AT314" s="3"/>
       <c r="AU314" s="3"/>
-    </row>
-    <row r="315" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV314" s="3"/>
+      <c r="AW314" s="3"/>
+      <c r="AX314" s="3"/>
+      <c r="AY314" s="3"/>
+    </row>
+    <row r="315" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -16636,53 +17941,10 @@
       <c r="AS315" s="3"/>
       <c r="AT315" s="3"/>
       <c r="AU315" s="3"/>
-    </row>
-    <row r="316" spans="3:47" x14ac:dyDescent="0.2">
-      <c r="C316" s="3"/>
-      <c r="D316" s="3"/>
-      <c r="E316" s="3"/>
-      <c r="F316" s="3"/>
-      <c r="G316" s="3"/>
-      <c r="H316" s="3"/>
-      <c r="I316" s="3"/>
-      <c r="J316" s="3"/>
-      <c r="K316" s="3"/>
-      <c r="L316" s="3"/>
-      <c r="M316" s="3"/>
-      <c r="N316" s="3"/>
-      <c r="O316" s="3"/>
-      <c r="P316" s="3"/>
-      <c r="Q316" s="3"/>
-      <c r="R316" s="3"/>
-      <c r="S316" s="3"/>
-      <c r="T316" s="3"/>
-      <c r="U316" s="3"/>
-      <c r="V316" s="3"/>
-      <c r="W316" s="3"/>
-      <c r="X316" s="3"/>
-      <c r="Y316" s="3"/>
-      <c r="Z316" s="3"/>
-      <c r="AA316" s="3"/>
-      <c r="AB316" s="3"/>
-      <c r="AC316" s="3"/>
-      <c r="AD316" s="3"/>
-      <c r="AE316" s="3"/>
-      <c r="AF316" s="3"/>
-      <c r="AG316" s="3"/>
-      <c r="AH316" s="3"/>
-      <c r="AI316" s="3"/>
-      <c r="AJ316" s="3"/>
-      <c r="AK316" s="3"/>
-      <c r="AL316" s="3"/>
-      <c r="AM316" s="3"/>
-      <c r="AN316" s="3"/>
-      <c r="AO316" s="3"/>
-      <c r="AP316" s="3"/>
-      <c r="AQ316" s="3"/>
-      <c r="AR316" s="3"/>
-      <c r="AS316" s="3"/>
-      <c r="AT316" s="3"/>
-      <c r="AU316" s="3"/>
+      <c r="AV315" s="3"/>
+      <c r="AW315" s="3"/>
+      <c r="AX315" s="3"/>
+      <c r="AY315" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/BIRK.xlsx
+++ b/BIRK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C863D295-C86A-419B-8A6B-3E4E4090B42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED565B9B-46AB-46E1-970A-B55D37A782FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{18F8973A-4B1D-45B3-BBD1-81233DF5C159}"/>
   </bookViews>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>FY25</t>
-  </si>
-  <si>
-    <t>Price</t>
   </si>
   <si>
     <t>Shares</t>
@@ -242,6 +239,9 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>Price EUR</t>
+  </si>
 </sst>
 </file>
 
@@ -250,13 +250,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -333,25 +339,29 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -705,32 +715,32 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I2" s="2">
-        <v>39.659999999999997</v>
+        <v>34.32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H3" s="2" t="s">
-        <v>20</v>
+      <c r="H3" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="I3" s="11">
         <f>+I2*I10</f>
-        <v>33.710999999999999</v>
+        <v>29.172000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" s="3">
         <v>183.90605600000001</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="15" t="s">
         <v>64</v>
       </c>
     </row>
@@ -739,11 +749,11 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" s="3">
         <f>+I3*I4</f>
-        <v>6199.6570538160004</v>
+        <v>5364.9074656319999</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -751,39 +761,39 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3">
-        <v>229.227</v>
-      </c>
-      <c r="J6" s="13" t="s">
+        <v>201.46700000000001</v>
+      </c>
+      <c r="J6" s="15" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3">
-        <f>1128.819+11.389</f>
-        <v>1140.2079999999999</v>
-      </c>
-      <c r="J7" s="13" t="s">
+        <f>1131.758+16.91</f>
+        <v>1148.6680000000001</v>
+      </c>
+      <c r="J7" s="15" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3">
         <f>+I5-I6+I7</f>
-        <v>7110.6380538160001</v>
+        <v>6312.1084656319999</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I10" s="2">
         <v>0.85</v>
@@ -791,42 +801,42 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H11" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H12" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>62</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J16" s="12"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -878,16 +888,16 @@
         <v>11</v>
       </c>
       <c r="K2" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="M2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="N2" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>67</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="s">
@@ -917,7 +927,7 @@
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3">
         <v>140.41</v>
@@ -948,7 +958,9 @@
       <c r="K3" s="3">
         <v>215.12299999999999</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>471.67</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -999,7 +1011,7 @@
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3">
         <v>160.655</v>
@@ -1030,7 +1042,9 @@
       <c r="K4" s="3">
         <v>186.18700000000001</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <v>146.381</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -1081,7 +1095,7 @@
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3">
         <v>181.453</v>
@@ -1112,7 +1126,9 @@
       <c r="K5" s="3">
         <v>221.774</v>
       </c>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>324.35899999999998</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -1163,7 +1179,7 @@
     </row>
     <row r="6" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3">
         <v>87.528000000000006</v>
@@ -1194,7 +1210,9 @@
       <c r="K6" s="3">
         <v>119.218</v>
       </c>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>235.131</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1245,7 +1263,7 @@
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3">
         <v>32.084000000000003</v>
@@ -1276,7 +1294,9 @@
       <c r="K7" s="3">
         <v>60.317999999999998</v>
       </c>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>58.561</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -1327,7 +1347,7 @@
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3">
         <v>1.859</v>
@@ -1358,7 +1378,9 @@
       <c r="K8" s="3">
         <v>0.59099999999999997</v>
       </c>
-      <c r="L8" s="3"/>
+      <c r="L8" s="3">
+        <v>0.28199999999999997</v>
+      </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -1409,7 +1431,7 @@
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="7">
         <v>302.92399999999998</v>
@@ -1440,7 +1462,9 @@
       <c r="K9" s="7">
         <v>401.90199999999999</v>
       </c>
-      <c r="L9" s="7"/>
+      <c r="L9" s="7">
+        <v>618.33299999999997</v>
+      </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -1507,7 +1531,7 @@
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3">
         <v>118.056</v>
@@ -1538,7 +1562,9 @@
       <c r="K10" s="3">
         <v>177.95599999999999</v>
       </c>
-      <c r="L10" s="3"/>
+      <c r="L10" s="3">
+        <v>284.77999999999997</v>
+      </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -1589,10 +1615,10 @@
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" ref="C11:K11" si="3">+C9-C10</f>
+        <f t="shared" ref="C11:L11" si="3">+C9-C10</f>
         <v>184.86799999999999</v>
       </c>
       <c r="D11" s="3">
@@ -1627,7 +1653,10 @@
         <f t="shared" si="3"/>
         <v>223.946</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <f t="shared" si="3"/>
+        <v>333.553</v>
+      </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -1694,7 +1723,7 @@
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3">
         <v>103.48399999999999</v>
@@ -1725,7 +1754,9 @@
       <c r="K12" s="3">
         <v>125.58</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>138.31100000000001</v>
+      </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -1776,7 +1807,7 @@
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3">
         <v>34.390999999999998</v>
@@ -1807,7 +1838,9 @@
       <c r="K13" s="3">
         <v>29.265999999999998</v>
       </c>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <v>32.973999999999997</v>
+      </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -1858,7 +1891,7 @@
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3">
         <v>11.654999999999999</v>
@@ -1889,7 +1922,9 @@
       <c r="K14" s="3">
         <v>3.238</v>
       </c>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>6.9530000000000003</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -1940,7 +1975,7 @@
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3">
         <v>0.23200000000000001</v>
@@ -1971,7 +2006,9 @@
       <c r="K15" s="3">
         <v>12.472</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>0.13500000000000001</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -2022,10 +2059,10 @@
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" ref="C16:K16" si="6">+C11-SUM(C12:C14)+C15</f>
+        <f t="shared" ref="C16:L16" si="6">+C11-SUM(C12:C14)+C15</f>
         <v>35.569999999999993</v>
       </c>
       <c r="D16" s="3">
@@ -2060,7 +2097,10 @@
         <f t="shared" si="6"/>
         <v>78.333999999999989</v>
       </c>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3">
+        <f t="shared" si="6"/>
+        <v>155.44999999999999</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -2127,7 +2167,7 @@
     </row>
     <row r="17" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3">
         <v>36.049999999999997</v>
@@ -2158,7 +2198,9 @@
       <c r="K17" s="3">
         <v>9.1489999999999991</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="3">
+        <v>33.805</v>
+      </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -2209,10 +2251,10 @@
     </row>
     <row r="18" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" ref="C18:K18" si="9">+C16-C17</f>
+        <f t="shared" ref="C18:L18" si="9">+C16-C17</f>
         <v>-0.48000000000000398</v>
       </c>
       <c r="D18" s="3">
@@ -2247,7 +2289,10 @@
         <f t="shared" si="9"/>
         <v>69.184999999999988</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3">
+        <f t="shared" si="9"/>
+        <v>121.64499999999998</v>
+      </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -2314,7 +2359,7 @@
     </row>
     <row r="19" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3">
         <v>6.6740000000000004</v>
@@ -2345,7 +2390,9 @@
       <c r="K19" s="3">
         <v>18.626999999999999</v>
       </c>
-      <c r="L19" s="3"/>
+      <c r="L19" s="3">
+        <v>39.762</v>
+      </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -2396,10 +2443,10 @@
     </row>
     <row r="20" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:K20" si="13">+C18-C19</f>
+        <f t="shared" ref="C20:L20" si="13">+C18-C19</f>
         <v>-7.1540000000000044</v>
       </c>
       <c r="D20" s="3">
@@ -2434,7 +2481,10 @@
         <f t="shared" si="13"/>
         <v>50.557999999999993</v>
       </c>
-      <c r="L20" s="3"/>
+      <c r="L20" s="3">
+        <f t="shared" si="13"/>
+        <v>81.882999999999981</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -2552,10 +2602,10 @@
     </row>
     <row r="22" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:K22" si="16">+C20/C23</f>
+        <f t="shared" ref="C22:L22" si="16">+C20/C23</f>
         <v>-3.8273026460271399E-2</v>
       </c>
       <c r="D22" s="8">
@@ -2590,7 +2640,10 @@
         <f t="shared" si="16"/>
         <v>0.27491209968637459</v>
       </c>
-      <c r="L22" s="8"/>
+      <c r="L22" s="8">
+        <f t="shared" si="16"/>
+        <v>0.44524363025870112</v>
+      </c>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="3"/>
@@ -2657,7 +2710,7 @@
     </row>
     <row r="23" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="3">
         <v>186.920154</v>
@@ -2687,7 +2740,9 @@
       <c r="K23" s="3">
         <v>183.90605600000001</v>
       </c>
-      <c r="L23" s="3"/>
+      <c r="L23" s="3">
+        <v>183.90605600000001</v>
+      </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -2789,7 +2844,7 @@
     </row>
     <row r="25" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -2800,7 +2855,7 @@
         <v>0.16118223451802938</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:K27" si="18">+H5/D5-1</f>
+        <f t="shared" ref="H25:L27" si="18">+H5/D5-1</f>
         <v>0.23018665910898028</v>
       </c>
       <c r="I25" s="9">
@@ -2815,7 +2870,10 @@
         <f t="shared" si="18"/>
         <v>5.2558139534883752E-2</v>
       </c>
-      <c r="L25" s="9"/>
+      <c r="L25" s="9">
+        <f t="shared" si="18"/>
+        <v>3.7869091653760956E-2</v>
+      </c>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
       <c r="O25" s="3"/>
@@ -2879,7 +2937,7 @@
     </row>
     <row r="26" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -2905,7 +2963,10 @@
         <f t="shared" si="18"/>
         <v>0.16017088527525569</v>
       </c>
-      <c r="L26" s="9"/>
+      <c r="L26" s="9">
+        <f t="shared" si="18"/>
+        <v>0.10470530198031436</v>
+      </c>
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
       <c r="O26" s="3"/>
@@ -2969,7 +3030,7 @@
     </row>
     <row r="27" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -2995,7 +3056,10 @@
         <f t="shared" si="18"/>
         <v>0.28055537863830327</v>
       </c>
-      <c r="L27" s="9"/>
+      <c r="L27" s="9">
+        <f t="shared" si="18"/>
+        <v>0.2246131325805103</v>
+      </c>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
       <c r="O27" s="3"/>
@@ -3059,7 +3123,7 @@
     </row>
     <row r="28" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -3085,37 +3149,40 @@
         <f>+K9/G9-1</f>
         <v>0.1110889944957274</v>
       </c>
-      <c r="L28" s="10"/>
+      <c r="L28" s="10">
+        <f>+L9/H9-1</f>
+        <v>7.6616231086657383E-2</v>
+      </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="10" t="e">
-        <f>+Q9/P9-1</f>
+        <f t="shared" ref="Q28:W28" si="22">+Q9/P9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R28" s="10" t="e">
-        <f>+R9/Q9-1</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S28" s="10" t="e">
-        <f>+S9/R9-1</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T28" s="10" t="e">
-        <f>+T9/S9-1</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U28" s="10">
-        <f>+U9/T9-1</f>
+        <f t="shared" si="22"/>
         <v>0.20041147925747071</v>
       </c>
       <c r="V28" s="10">
-        <f>+V9/U9-1</f>
+        <f t="shared" si="22"/>
         <v>0.20964990538979866</v>
       </c>
       <c r="W28" s="10">
-        <f>+W9/V9-1</f>
+        <f t="shared" si="22"/>
         <v>0.16221013027168119</v>
       </c>
       <c r="X28" s="3"/>
@@ -3149,22 +3216,22 @@
     </row>
     <row r="29" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="22">+C11/C9</f>
+        <f t="shared" ref="C29:F29" si="23">+C11/C9</f>
         <v>0.61027848569278109</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.56345637556000705</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.59481229128228386</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.58961216770082747</v>
       </c>
       <c r="G29" s="9">
@@ -3187,40 +3254,43 @@
         <f>+K11/K9</f>
         <v>0.55721544058004191</v>
       </c>
-      <c r="L29" s="9"/>
+      <c r="L29" s="9">
+        <f>+L11/L9</f>
+        <v>0.53943910481892443</v>
+      </c>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
       <c r="O29" s="3"/>
       <c r="P29" s="9" t="e">
-        <f t="shared" ref="P29:W29" si="23">+P11/P9</f>
+        <f t="shared" ref="P29:W29" si="24">+P11/P9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q29" s="9" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R29" s="9" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S29" s="9" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.60330068480640597</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.62054170791689311</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.58773362738198787</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.59105981656590045</v>
       </c>
       <c r="X29" s="3"/>
@@ -3254,22 +3324,22 @@
     </row>
     <row r="30" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:F30" si="24">+C16/C9</f>
+        <f t="shared" ref="C30:F30" si="25">+C16/C9</f>
         <v>0.11742219170485005</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.27535096541463377</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.27529136373455537</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.21398794112742545</v>
       </c>
       <c r="G30" s="9">
@@ -3292,40 +3362,43 @@
         <f>+K16/K9</f>
         <v>0.19490821145453366</v>
       </c>
-      <c r="L30" s="9"/>
+      <c r="L30" s="9">
+        <f>+L16/L9</f>
+        <v>0.25140175277722521</v>
+      </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
       <c r="O30" s="3"/>
       <c r="P30" s="9" t="e">
-        <f t="shared" ref="P30:W30" si="25">+P16/P9</f>
+        <f t="shared" ref="P30:W30" si="26">+P16/P9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q30" s="9" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R30" s="9" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S30" s="9" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.29209636371097319</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.17473428374748889</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.23332649928796623</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.26200839217918703</v>
       </c>
       <c r="X30" s="3"/>
@@ -3359,22 +3432,22 @@
     </row>
     <row r="31" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="26">+C19/C18</f>
+        <f t="shared" ref="C31:F31" si="27">+C19/C18</f>
         <v>-13.904166666666551</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.31839196362321864</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.3266648631588438</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.32986772317720037</v>
       </c>
       <c r="G31" s="9">
@@ -3397,40 +3470,43 @@
         <f>+K19/K18</f>
         <v>0.26923466069234664</v>
       </c>
-      <c r="L31" s="9"/>
+      <c r="L31" s="9">
+        <f>+L19/L18</f>
+        <v>0.32686916848205849</v>
+      </c>
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
       <c r="O31" s="3"/>
       <c r="P31" s="9" t="e">
-        <f t="shared" ref="P31:W31" si="27">+P19/P18</f>
+        <f t="shared" ref="P31:W31" si="28">+P19/P18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q31" s="9" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R31" s="9" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S31" s="9" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.25312145742523673</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.51174081691094186</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.34780891953897825</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.25884718498659509</v>
       </c>
       <c r="X31" s="3"/>
